--- a/research/traditional_assets/database/data/kuwait/kuwait_power.xlsx
+++ b/research/traditional_assets/database/data/kuwait/kuwait_power.xlsx
@@ -1266,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1403,22 +1403,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.06928487337826286</v>
+        <v>0.06921919606819545</v>
       </c>
       <c r="C2">
-        <v>1673.968805906716</v>
+        <v>1660.558763010748</v>
       </c>
       <c r="D2">
-        <v>1629.468805906716</v>
+        <v>1631.643763010748</v>
       </c>
       <c r="E2">
-        <v>-1019.6</v>
+        <v>-1004.015</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>15.585</v>
       </c>
       <c r="G2">
         <v>44.5</v>
@@ -1439,28 +1439,28 @@
         <v>154.9666666666667</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.7839255000000001</v>
       </c>
       <c r="N2">
-        <v>154.9666666666667</v>
+        <v>154.1827411666667</v>
       </c>
       <c r="O2">
-        <v>23.245</v>
+        <v>23.127411175</v>
       </c>
       <c r="P2">
-        <v>131.7216666666667</v>
+        <v>131.0553299916667</v>
       </c>
       <c r="Q2">
-        <v>131.9216666666667</v>
+        <v>131.2553299916667</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.06928487337826286</v>
+        <v>0.06948651117999541</v>
       </c>
       <c r="T2">
-        <v>0.4454993697880389</v>
+        <v>0.4493243643771281</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>197.6803493019001</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1485,22 +1485,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.06921919606819545</v>
+        <v>0.06915351875812806</v>
       </c>
       <c r="C3">
-        <v>1660.558763010748</v>
+        <v>1647.15453398596</v>
       </c>
       <c r="D3">
-        <v>1631.643763010748</v>
+        <v>1633.82453398596</v>
       </c>
       <c r="E3">
-        <v>-1004.015</v>
+        <v>-988.4300000000001</v>
       </c>
       <c r="F3">
-        <v>15.585</v>
+        <v>31.17</v>
       </c>
       <c r="G3">
         <v>44.5</v>
@@ -1521,28 +1521,28 @@
         <v>154.9666666666667</v>
       </c>
       <c r="M3">
-        <v>0.7839255000000001</v>
+        <v>1.567851</v>
       </c>
       <c r="N3">
-        <v>154.1827411666667</v>
+        <v>153.3988156666667</v>
       </c>
       <c r="O3">
-        <v>23.127411175</v>
+        <v>23.00982235</v>
       </c>
       <c r="P3">
-        <v>131.0553299916667</v>
+        <v>130.3889933166667</v>
       </c>
       <c r="Q3">
-        <v>131.2553299916667</v>
+        <v>130.5889933166667</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.06948651117999541</v>
+        <v>0.06969226403890619</v>
       </c>
       <c r="T3">
-        <v>0.4493243643771281</v>
+        <v>0.4532274200802805</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>197.6803493019001</v>
+        <v>98.84017465095003</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1567,22 +1567,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.06915351875812806</v>
+        <v>0.06908784144806066</v>
       </c>
       <c r="C4">
-        <v>1647.15453398596</v>
+        <v>1633.756142175112</v>
       </c>
       <c r="D4">
-        <v>1633.82453398596</v>
+        <v>1636.011142175112</v>
       </c>
       <c r="E4">
-        <v>-988.4300000000001</v>
+        <v>-972.845</v>
       </c>
       <c r="F4">
-        <v>31.17</v>
+        <v>46.755</v>
       </c>
       <c r="G4">
         <v>44.5</v>
@@ -1603,28 +1603,28 @@
         <v>154.9666666666667</v>
       </c>
       <c r="M4">
-        <v>1.567851</v>
+        <v>2.3517765</v>
       </c>
       <c r="N4">
-        <v>153.3988156666667</v>
+        <v>152.6148901666667</v>
       </c>
       <c r="O4">
-        <v>23.00982235</v>
+        <v>22.892233525</v>
       </c>
       <c r="P4">
-        <v>130.3889933166667</v>
+        <v>129.7226566416667</v>
       </c>
       <c r="Q4">
-        <v>130.5889933166667</v>
+        <v>129.9226566416667</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.06969226403890619</v>
+        <v>0.06990225922480481</v>
       </c>
       <c r="T4">
-        <v>0.4532274200802805</v>
+        <v>0.4572109511587554</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>98.84017465095003</v>
+        <v>65.89344976730003</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1649,22 +1649,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.06908784144806066</v>
+        <v>0.06902216413799327</v>
       </c>
       <c r="C5">
-        <v>1633.756142175112</v>
+        <v>1620.363611046095</v>
       </c>
       <c r="D5">
-        <v>1636.011142175112</v>
+        <v>1638.203611046095</v>
       </c>
       <c r="E5">
-        <v>-972.845</v>
+        <v>-957.26</v>
       </c>
       <c r="F5">
-        <v>46.755</v>
+        <v>62.34</v>
       </c>
       <c r="G5">
         <v>44.5</v>
@@ -1685,28 +1685,28 @@
         <v>154.9666666666667</v>
       </c>
       <c r="M5">
-        <v>2.3517765</v>
+        <v>3.135702</v>
       </c>
       <c r="N5">
-        <v>152.6148901666667</v>
+        <v>151.8309646666667</v>
       </c>
       <c r="O5">
-        <v>22.892233525</v>
+        <v>22.7746447</v>
       </c>
       <c r="P5">
-        <v>129.7226566416667</v>
+        <v>129.0563199666666</v>
       </c>
       <c r="Q5">
-        <v>129.9226566416667</v>
+        <v>129.2563199666666</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.06990225922480481</v>
+        <v>0.07011662931040966</v>
       </c>
       <c r="T5">
-        <v>0.4572109511587554</v>
+        <v>0.461277472468032</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>65.89344976730003</v>
+        <v>49.42008732547502</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1731,22 +1731,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.06902216413799327</v>
+        <v>0.06895648682792588</v>
       </c>
       <c r="C6">
-        <v>1620.363611046095</v>
+        <v>1606.976964192768</v>
       </c>
       <c r="D6">
-        <v>1638.203611046095</v>
+        <v>1640.401964192768</v>
       </c>
       <c r="E6">
-        <v>-957.26</v>
+        <v>-941.675</v>
       </c>
       <c r="F6">
-        <v>62.34</v>
+        <v>77.92500000000001</v>
       </c>
       <c r="G6">
         <v>44.5</v>
@@ -1767,28 +1767,28 @@
         <v>154.9666666666667</v>
       </c>
       <c r="M6">
-        <v>3.135702</v>
+        <v>3.9196275</v>
       </c>
       <c r="N6">
-        <v>151.8309646666667</v>
+        <v>151.0470391666667</v>
       </c>
       <c r="O6">
-        <v>22.7746447</v>
+        <v>22.657055875</v>
       </c>
       <c r="P6">
-        <v>129.0563199666666</v>
+        <v>128.3899832916667</v>
       </c>
       <c r="Q6">
-        <v>129.2563199666666</v>
+        <v>128.5899832916667</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07011662931040966</v>
+        <v>0.07033551245044831</v>
       </c>
       <c r="T6">
-        <v>0.461277472468032</v>
+        <v>0.4654296047522407</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>49.42008732547502</v>
+        <v>39.53606986038002</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1813,22 +1813,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.06895648682792588</v>
+        <v>0.06889080951785849</v>
       </c>
       <c r="C7">
-        <v>1606.976964192768</v>
+        <v>1593.596225335804</v>
       </c>
       <c r="D7">
-        <v>1640.401964192768</v>
+        <v>1642.606225335804</v>
       </c>
       <c r="E7">
-        <v>-941.675</v>
+        <v>-926.09</v>
       </c>
       <c r="F7">
-        <v>77.92500000000001</v>
+        <v>93.51000000000001</v>
       </c>
       <c r="G7">
         <v>44.5</v>
@@ -1849,28 +1849,28 @@
         <v>154.9666666666667</v>
       </c>
       <c r="M7">
-        <v>3.9196275</v>
+        <v>4.703553</v>
       </c>
       <c r="N7">
-        <v>151.0470391666667</v>
+        <v>150.2631136666667</v>
       </c>
       <c r="O7">
-        <v>22.657055875</v>
+        <v>22.53946705</v>
       </c>
       <c r="P7">
-        <v>128.3899832916667</v>
+        <v>127.7236466166667</v>
       </c>
       <c r="Q7">
-        <v>128.5899832916667</v>
+        <v>127.9236466166667</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07033551245044831</v>
+        <v>0.07055905267857286</v>
       </c>
       <c r="T7">
-        <v>0.4654296047522407</v>
+        <v>0.4696700802765389</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>39.53606986038002</v>
+        <v>32.94672488365001</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1895,22 +1895,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.06889080951785848</v>
+        <v>0.0688251322077911</v>
       </c>
       <c r="C8">
-        <v>1593.596225335804</v>
+        <v>1580.221418323547</v>
       </c>
       <c r="D8">
-        <v>1642.606225335804</v>
+        <v>1644.816418323547</v>
       </c>
       <c r="E8">
-        <v>-926.09</v>
+        <v>-910.505</v>
       </c>
       <c r="F8">
-        <v>93.50999999999999</v>
+        <v>109.095</v>
       </c>
       <c r="G8">
         <v>44.5</v>
@@ -1931,28 +1931,28 @@
         <v>154.9666666666667</v>
       </c>
       <c r="M8">
-        <v>4.703552999999999</v>
+        <v>5.487478499999999</v>
       </c>
       <c r="N8">
-        <v>150.2631136666667</v>
+        <v>149.4791881666667</v>
       </c>
       <c r="O8">
-        <v>22.53946705</v>
+        <v>22.421878225</v>
       </c>
       <c r="P8">
-        <v>127.7236466166667</v>
+        <v>127.0573099416667</v>
       </c>
       <c r="Q8">
-        <v>127.9236466166667</v>
+        <v>127.2573099416666</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07055905267857286</v>
+        <v>0.07078740022343129</v>
       </c>
       <c r="T8">
-        <v>0.4696700802765389</v>
+        <v>0.4740017488228651</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>32.94672488365002</v>
+        <v>28.24004990027144</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.0688251322077911</v>
+        <v>0.0687594548977237</v>
       </c>
       <c r="C9">
-        <v>1580.221418323547</v>
+        <v>1566.852567132868</v>
       </c>
       <c r="D9">
-        <v>1644.816418323547</v>
+        <v>1647.032567132868</v>
       </c>
       <c r="E9">
-        <v>-910.505</v>
+        <v>-894.9200000000001</v>
       </c>
       <c r="F9">
-        <v>109.095</v>
+        <v>124.68</v>
       </c>
       <c r="G9">
         <v>44.5</v>
@@ -2013,28 +2013,28 @@
         <v>154.9666666666667</v>
       </c>
       <c r="M9">
-        <v>5.487478500000001</v>
+        <v>6.271404</v>
       </c>
       <c r="N9">
-        <v>149.4791881666667</v>
+        <v>148.6952626666667</v>
       </c>
       <c r="O9">
-        <v>22.421878225</v>
+        <v>22.3042894</v>
       </c>
       <c r="P9">
-        <v>127.0573099416667</v>
+        <v>126.3909732666667</v>
       </c>
       <c r="Q9">
-        <v>127.2573099416666</v>
+        <v>126.5909732666667</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.07078740022343129</v>
+        <v>0.07102071184535184</v>
       </c>
       <c r="T9">
-        <v>0.4740017488228651</v>
+        <v>0.4784275840767201</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>28.24004990027143</v>
+        <v>24.71004366273751</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2059,22 +2059,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.0687594548977237</v>
+        <v>0.06869377758765631</v>
       </c>
       <c r="C10">
-        <v>1566.852567132868</v>
+        <v>1553.489695870034</v>
       </c>
       <c r="D10">
-        <v>1647.032567132868</v>
+        <v>1649.254695870034</v>
       </c>
       <c r="E10">
-        <v>-894.9200000000001</v>
+        <v>-879.335</v>
       </c>
       <c r="F10">
-        <v>124.68</v>
+        <v>140.265</v>
       </c>
       <c r="G10">
         <v>44.5</v>
@@ -2095,28 +2095,28 @@
         <v>154.9666666666667</v>
       </c>
       <c r="M10">
-        <v>6.271404</v>
+        <v>7.055329499999999</v>
       </c>
       <c r="N10">
-        <v>148.6952626666667</v>
+        <v>147.9113371666667</v>
       </c>
       <c r="O10">
-        <v>22.3042894</v>
+        <v>22.186700575</v>
       </c>
       <c r="P10">
-        <v>126.3909732666667</v>
+        <v>125.7246365916667</v>
       </c>
       <c r="Q10">
-        <v>126.5909732666667</v>
+        <v>125.9246365916667</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07102071184535184</v>
+        <v>0.07125915119522672</v>
       </c>
       <c r="T10">
-        <v>0.4784275840767201</v>
+        <v>0.4829506904350554</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>24.71004366273751</v>
+        <v>21.96448325576668</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2141,22 +2141,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.06869377758765631</v>
+        <v>0.06862810027758892</v>
       </c>
       <c r="C11">
-        <v>1553.489695870034</v>
+        <v>1540.132828771582</v>
       </c>
       <c r="D11">
-        <v>1649.254695870034</v>
+        <v>1651.482828771582</v>
       </c>
       <c r="E11">
-        <v>-879.335</v>
+        <v>-863.75</v>
       </c>
       <c r="F11">
-        <v>140.265</v>
+        <v>155.85</v>
       </c>
       <c r="G11">
         <v>44.5</v>
@@ -2177,28 +2177,28 @@
         <v>154.9666666666667</v>
       </c>
       <c r="M11">
-        <v>7.055329499999999</v>
+        <v>7.839255</v>
       </c>
       <c r="N11">
-        <v>147.9113371666667</v>
+        <v>147.1274116666667</v>
       </c>
       <c r="O11">
-        <v>22.186700575</v>
+        <v>22.06911175</v>
       </c>
       <c r="P11">
-        <v>125.7246365916667</v>
+        <v>125.0582999166667</v>
       </c>
       <c r="Q11">
-        <v>125.9246365916667</v>
+        <v>125.2582999166667</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07125915119522672</v>
+        <v>0.07150288919732102</v>
       </c>
       <c r="T11">
-        <v>0.4829506904350554</v>
+        <v>0.4875743102680204</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>21.96448325576668</v>
+        <v>19.76803493019001</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2223,22 +2223,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.06862810027758892</v>
+        <v>0.06856242296752152</v>
       </c>
       <c r="C12">
-        <v>1540.132828771582</v>
+        <v>1526.7819902052</v>
       </c>
       <c r="D12">
-        <v>1651.482828771582</v>
+        <v>1653.7169902052</v>
       </c>
       <c r="E12">
-        <v>-863.75</v>
+        <v>-848.165</v>
       </c>
       <c r="F12">
-        <v>155.85</v>
+        <v>171.435</v>
       </c>
       <c r="G12">
         <v>44.5</v>
@@ -2259,28 +2259,28 @@
         <v>154.9666666666667</v>
       </c>
       <c r="M12">
-        <v>7.839255000000001</v>
+        <v>8.6231805</v>
       </c>
       <c r="N12">
-        <v>147.1274116666667</v>
+        <v>146.3434861666667</v>
       </c>
       <c r="O12">
-        <v>22.06911175</v>
+        <v>21.951522925</v>
       </c>
       <c r="P12">
-        <v>125.0582999166667</v>
+        <v>124.3919632416667</v>
       </c>
       <c r="Q12">
-        <v>125.2582999166667</v>
+        <v>124.5919632416667</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07150288919732102</v>
+        <v>0.07175210445788935</v>
       </c>
       <c r="T12">
-        <v>0.4875743102680204</v>
+        <v>0.4923018316702655</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>19.76803493019001</v>
+        <v>17.97094084562728</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2305,22 +2305,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.06856242296752152</v>
+        <v>0.06849674565745412</v>
       </c>
       <c r="C13">
-        <v>1526.7819902052</v>
+        <v>1513.437204670614</v>
       </c>
       <c r="D13">
-        <v>1653.7169902052</v>
+        <v>1655.957204670614</v>
       </c>
       <c r="E13">
-        <v>-848.165</v>
+        <v>-832.58</v>
       </c>
       <c r="F13">
-        <v>171.435</v>
+        <v>187.02</v>
       </c>
       <c r="G13">
         <v>44.5</v>
@@ -2341,28 +2341,28 @@
         <v>154.9666666666667</v>
       </c>
       <c r="M13">
-        <v>8.6231805</v>
+        <v>9.407105999999999</v>
       </c>
       <c r="N13">
-        <v>146.3434861666667</v>
+        <v>145.5595606666667</v>
       </c>
       <c r="O13">
-        <v>21.951522925</v>
+        <v>21.8339341</v>
       </c>
       <c r="P13">
-        <v>124.3919632416667</v>
+        <v>123.7256265666667</v>
       </c>
       <c r="Q13">
-        <v>124.5919632416667</v>
+        <v>123.9256265666667</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.07175210445788935</v>
+        <v>0.07200698370165241</v>
       </c>
       <c r="T13">
-        <v>0.4923018316702655</v>
+        <v>0.4971367967407435</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>17.97094084562728</v>
+        <v>16.47336244182501</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2387,22 +2387,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.06849674565745412</v>
+        <v>0.06843106834738673</v>
       </c>
       <c r="C14">
-        <v>1513.437204670614</v>
+        <v>1500.098496800484</v>
       </c>
       <c r="D14">
-        <v>1655.957204670614</v>
+        <v>1658.203496800484</v>
       </c>
       <c r="E14">
-        <v>-832.58</v>
+        <v>-816.995</v>
       </c>
       <c r="F14">
-        <v>187.02</v>
+        <v>202.605</v>
       </c>
       <c r="G14">
         <v>44.5</v>
@@ -2423,28 +2423,28 @@
         <v>154.9666666666667</v>
       </c>
       <c r="M14">
-        <v>9.407105999999999</v>
+        <v>10.1910315</v>
       </c>
       <c r="N14">
-        <v>145.5595606666667</v>
+        <v>144.7756351666667</v>
       </c>
       <c r="O14">
-        <v>21.8339341</v>
+        <v>21.716345275</v>
       </c>
       <c r="P14">
-        <v>123.7256265666667</v>
+        <v>123.0592898916667</v>
       </c>
       <c r="Q14">
-        <v>123.9256265666667</v>
+        <v>123.2592898916667</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.07200698370165241</v>
+        <v>0.07226772223837555</v>
       </c>
       <c r="T14">
-        <v>0.4971367967407435</v>
+        <v>0.5020829104335313</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>16.47336244182501</v>
+        <v>15.20618071553077</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2469,22 +2469,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.06843106834738673</v>
+        <v>0.06836539103731933</v>
       </c>
       <c r="C15">
-        <v>1500.098496800484</v>
+        <v>1486.765891361312</v>
       </c>
       <c r="D15">
-        <v>1658.203496800484</v>
+        <v>1660.455891361312</v>
       </c>
       <c r="E15">
-        <v>-816.995</v>
+        <v>-801.41</v>
       </c>
       <c r="F15">
-        <v>202.605</v>
+        <v>218.19</v>
       </c>
       <c r="G15">
         <v>44.5</v>
@@ -2505,28 +2505,28 @@
         <v>154.9666666666667</v>
       </c>
       <c r="M15">
-        <v>10.1910315</v>
+        <v>10.974957</v>
       </c>
       <c r="N15">
-        <v>144.7756351666667</v>
+        <v>143.9917096666667</v>
       </c>
       <c r="O15">
-        <v>21.716345275</v>
+        <v>21.59875645</v>
       </c>
       <c r="P15">
-        <v>123.0592898916667</v>
+        <v>122.3929532166667</v>
       </c>
       <c r="Q15">
-        <v>123.2592898916667</v>
+        <v>122.5929532166667</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.07226772223837555</v>
+        <v>0.07253452446199922</v>
       </c>
       <c r="T15">
-        <v>0.5020829104335313</v>
+        <v>0.5071440500261513</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2543,7 +2543,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>15.20618071553077</v>
+        <v>14.12002495013572</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2551,22 +2551,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.06836539103731933</v>
+        <v>0.06829971372725194</v>
       </c>
       <c r="C16">
-        <v>1486.765891361312</v>
+        <v>1473.439413254342</v>
       </c>
       <c r="D16">
-        <v>1660.455891361312</v>
+        <v>1662.714413254342</v>
       </c>
       <c r="E16">
-        <v>-801.41</v>
+        <v>-785.825</v>
       </c>
       <c r="F16">
-        <v>218.19</v>
+        <v>233.775</v>
       </c>
       <c r="G16">
         <v>44.5</v>
@@ -2587,28 +2587,28 @@
         <v>154.9666666666667</v>
       </c>
       <c r="M16">
-        <v>10.974957</v>
+        <v>11.7588825</v>
       </c>
       <c r="N16">
-        <v>143.9917096666667</v>
+        <v>143.2077841666667</v>
       </c>
       <c r="O16">
-        <v>21.59875645</v>
+        <v>21.481167625</v>
       </c>
       <c r="P16">
-        <v>122.3929532166667</v>
+        <v>121.7266165416667</v>
       </c>
       <c r="Q16">
-        <v>122.5929532166667</v>
+        <v>121.9266165416667</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.07253452446199922</v>
+        <v>0.07280760438500228</v>
       </c>
       <c r="T16">
-        <v>0.5071440500261513</v>
+        <v>0.5123242752562448</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2625,7 +2625,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>14.12002495013572</v>
+        <v>13.17868995346</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2633,22 +2633,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.06829971372725194</v>
+        <v>0.06843803641718454</v>
       </c>
       <c r="C17">
-        <v>1473.439413254342</v>
+        <v>1453.104886278894</v>
       </c>
       <c r="D17">
-        <v>1662.714413254342</v>
+        <v>1657.964886278894</v>
       </c>
       <c r="E17">
-        <v>-785.825</v>
+        <v>-770.24</v>
       </c>
       <c r="F17">
-        <v>233.775</v>
+        <v>249.36</v>
       </c>
       <c r="G17">
         <v>44.5</v>
@@ -2669,45 +2669,45 @@
         <v>154.9666666666667</v>
       </c>
       <c r="M17">
-        <v>11.7588825</v>
+        <v>12.916848</v>
       </c>
       <c r="N17">
-        <v>143.2077841666667</v>
+        <v>142.0498186666667</v>
       </c>
       <c r="O17">
-        <v>21.481167625</v>
+        <v>21.3074728</v>
       </c>
       <c r="P17">
-        <v>121.7266165416667</v>
+        <v>120.7423458666667</v>
       </c>
       <c r="Q17">
-        <v>121.9266165416667</v>
+        <v>120.9423458666667</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.07280760438500228</v>
+        <v>0.07308718621093399</v>
       </c>
       <c r="T17">
-        <v>0.5123242752562448</v>
+        <v>0.5176278391822929</v>
       </c>
       <c r="U17">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V17">
         <v>0.15</v>
       </c>
       <c r="W17">
-        <v>0.04275499999999999</v>
+        <v>0.04403</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y17">
-        <v>13.17868995346001</v>
+        <v>11.99725092891599</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2715,22 +2715,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.06843803641718454</v>
+        <v>0.06838510910711715</v>
       </c>
       <c r="C18">
-        <v>1453.104886278894</v>
+        <v>1439.334020284967</v>
       </c>
       <c r="D18">
-        <v>1657.964886278894</v>
+        <v>1659.779020284967</v>
       </c>
       <c r="E18">
-        <v>-770.24</v>
+        <v>-754.655</v>
       </c>
       <c r="F18">
-        <v>249.36</v>
+        <v>264.945</v>
       </c>
       <c r="G18">
         <v>44.5</v>
@@ -2751,28 +2751,28 @@
         <v>154.9666666666667</v>
       </c>
       <c r="M18">
-        <v>12.916848</v>
+        <v>13.724151</v>
       </c>
       <c r="N18">
-        <v>142.0498186666667</v>
+        <v>141.2425156666667</v>
       </c>
       <c r="O18">
-        <v>21.3074728</v>
+        <v>21.18637735</v>
       </c>
       <c r="P18">
-        <v>120.7423458666667</v>
+        <v>120.0561383166667</v>
       </c>
       <c r="Q18">
-        <v>120.9423458666667</v>
+        <v>120.2561383166667</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.07308718621093399</v>
+        <v>0.07337350494833392</v>
       </c>
       <c r="T18">
-        <v>0.5176278391822929</v>
+        <v>0.5230591998294506</v>
       </c>
       <c r="U18">
         <v>0.0518</v>
@@ -2789,7 +2789,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>11.99725092891599</v>
+        <v>11.29153028603858</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2797,22 +2797,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.06838510910711715</v>
+        <v>0.06833218179704975</v>
       </c>
       <c r="C19">
-        <v>1439.334020284967</v>
+        <v>1425.567128666184</v>
       </c>
       <c r="D19">
-        <v>1659.779020284967</v>
+        <v>1661.597128666184</v>
       </c>
       <c r="E19">
-        <v>-754.655</v>
+        <v>-739.0699999999999</v>
       </c>
       <c r="F19">
-        <v>264.945</v>
+        <v>280.53</v>
       </c>
       <c r="G19">
         <v>44.5</v>
@@ -2833,28 +2833,28 @@
         <v>154.9666666666667</v>
       </c>
       <c r="M19">
-        <v>13.724151</v>
+        <v>14.531454</v>
       </c>
       <c r="N19">
-        <v>141.2425156666667</v>
+        <v>140.4352126666667</v>
       </c>
       <c r="O19">
-        <v>21.18637735</v>
+        <v>21.0652819</v>
       </c>
       <c r="P19">
-        <v>120.0561383166667</v>
+        <v>119.3699307666667</v>
       </c>
       <c r="Q19">
-        <v>120.2561383166667</v>
+        <v>119.5699307666667</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.07337350494833392</v>
+        <v>0.07366680706957288</v>
       </c>
       <c r="T19">
-        <v>0.5230591998294506</v>
+        <v>0.5286230326875144</v>
       </c>
       <c r="U19">
         <v>0.0518</v>
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>11.29153028603858</v>
+        <v>10.66422304792533</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2879,22 +2879,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.06833218179704977</v>
+        <v>0.06827925448698235</v>
       </c>
       <c r="C20">
-        <v>1425.567128666183</v>
+        <v>1411.804224497361</v>
       </c>
       <c r="D20">
-        <v>1661.597128666183</v>
+        <v>1663.419224497361</v>
       </c>
       <c r="E20">
-        <v>-739.0700000000001</v>
+        <v>-723.485</v>
       </c>
       <c r="F20">
-        <v>280.53</v>
+        <v>296.115</v>
       </c>
       <c r="G20">
         <v>44.5</v>
@@ -2915,28 +2915,28 @@
         <v>154.9666666666667</v>
       </c>
       <c r="M20">
-        <v>14.531454</v>
+        <v>15.338757</v>
       </c>
       <c r="N20">
-        <v>140.4352126666667</v>
+        <v>139.6279096666667</v>
       </c>
       <c r="O20">
-        <v>21.0652819</v>
+        <v>20.94418645</v>
       </c>
       <c r="P20">
-        <v>119.3699307666667</v>
+        <v>118.6837232166667</v>
       </c>
       <c r="Q20">
-        <v>119.5699307666667</v>
+        <v>118.8837232166667</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.07366680706957288</v>
+        <v>0.07396735121849674</v>
       </c>
       <c r="T20">
-        <v>0.5286230326875144</v>
+        <v>0.5343242441346664</v>
       </c>
       <c r="U20">
         <v>0.0518</v>
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>10.66422304792533</v>
+        <v>10.1029481506661</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2961,22 +2961,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.06827925448698235</v>
+        <v>0.06851532717691497</v>
       </c>
       <c r="C21">
-        <v>1411.804224497361</v>
+        <v>1388.122784519356</v>
       </c>
       <c r="D21">
-        <v>1663.419224497361</v>
+        <v>1655.322784519356</v>
       </c>
       <c r="E21">
-        <v>-723.485</v>
+        <v>-707.9</v>
       </c>
       <c r="F21">
-        <v>296.115</v>
+        <v>311.7</v>
       </c>
       <c r="G21">
         <v>44.5</v>
@@ -2997,45 +2997,45 @@
         <v>154.9666666666667</v>
       </c>
       <c r="M21">
-        <v>15.338757</v>
+        <v>16.67595</v>
       </c>
       <c r="N21">
-        <v>139.6279096666667</v>
+        <v>138.2907166666667</v>
       </c>
       <c r="O21">
-        <v>20.94418645</v>
+        <v>20.7436075</v>
       </c>
       <c r="P21">
-        <v>118.6837232166667</v>
+        <v>117.5471091666667</v>
       </c>
       <c r="Q21">
-        <v>118.8837232166667</v>
+        <v>117.7471091666667</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.07396735121849674</v>
+        <v>0.07427540897114371</v>
       </c>
       <c r="T21">
-        <v>0.5343242441346664</v>
+        <v>0.5401679858679972</v>
       </c>
       <c r="U21">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V21">
         <v>0.15</v>
       </c>
       <c r="W21">
-        <v>0.04403</v>
+        <v>0.04547499999999999</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y21">
-        <v>10.1029481506661</v>
+        <v>9.292823897089319</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.06851532717691497</v>
+        <v>0.06847684986684757</v>
       </c>
       <c r="C22">
-        <v>1388.122784519356</v>
+        <v>1373.85203669652</v>
       </c>
       <c r="D22">
-        <v>1655.322784519356</v>
+        <v>1656.63703669652</v>
       </c>
       <c r="E22">
-        <v>-707.9</v>
+        <v>-692.3150000000001</v>
       </c>
       <c r="F22">
-        <v>311.7</v>
+        <v>327.285</v>
       </c>
       <c r="G22">
         <v>44.5</v>
@@ -3079,28 +3079,28 @@
         <v>154.9666666666667</v>
       </c>
       <c r="M22">
-        <v>16.67595</v>
+        <v>17.5097475</v>
       </c>
       <c r="N22">
-        <v>138.2907166666667</v>
+        <v>137.4569191666667</v>
       </c>
       <c r="O22">
-        <v>20.7436075</v>
+        <v>20.618537875</v>
       </c>
       <c r="P22">
-        <v>117.5471091666667</v>
+        <v>116.8383812916667</v>
       </c>
       <c r="Q22">
-        <v>117.7471091666667</v>
+        <v>117.0383812916667</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.07427540897114371</v>
+        <v>0.07459126565423743</v>
       </c>
       <c r="T22">
-        <v>0.5401679858679972</v>
+        <v>0.5461596704300199</v>
       </c>
       <c r="U22">
         <v>0.0535</v>
@@ -3117,7 +3117,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>9.292823897089319</v>
+        <v>8.850308473418401</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3125,22 +3125,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.06847684986684757</v>
+        <v>0.06843837255678017</v>
       </c>
       <c r="C23">
-        <v>1373.85203669652</v>
+        <v>1359.583377446689</v>
       </c>
       <c r="D23">
-        <v>1656.63703669652</v>
+        <v>1657.953377446689</v>
       </c>
       <c r="E23">
-        <v>-692.3150000000001</v>
+        <v>-676.73</v>
       </c>
       <c r="F23">
-        <v>327.285</v>
+        <v>342.87</v>
       </c>
       <c r="G23">
         <v>44.5</v>
@@ -3161,28 +3161,28 @@
         <v>154.9666666666667</v>
       </c>
       <c r="M23">
-        <v>17.5097475</v>
+        <v>18.343545</v>
       </c>
       <c r="N23">
-        <v>137.4569191666667</v>
+        <v>136.6231216666667</v>
       </c>
       <c r="O23">
-        <v>20.618537875</v>
+        <v>20.49346825</v>
       </c>
       <c r="P23">
-        <v>116.8383812916667</v>
+        <v>116.1296534166667</v>
       </c>
       <c r="Q23">
-        <v>117.0383812916667</v>
+        <v>116.3296534166666</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.07459126565423743</v>
+        <v>0.07491522122664125</v>
       </c>
       <c r="T23">
-        <v>0.5461596704300199</v>
+        <v>0.5523049879295303</v>
       </c>
       <c r="U23">
         <v>0.0535</v>
@@ -3199,7 +3199,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>8.850308473418401</v>
+        <v>8.448021724626656</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3207,22 +3207,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.06843837255678017</v>
+        <v>0.06839989524671278</v>
       </c>
       <c r="C24">
-        <v>1359.583377446689</v>
+        <v>1345.316811752474</v>
       </c>
       <c r="D24">
-        <v>1657.953377446689</v>
+        <v>1659.271811752474</v>
       </c>
       <c r="E24">
-        <v>-676.73</v>
+        <v>-661.145</v>
       </c>
       <c r="F24">
-        <v>342.87</v>
+        <v>358.455</v>
       </c>
       <c r="G24">
         <v>44.5</v>
@@ -3243,28 +3243,28 @@
         <v>154.9666666666667</v>
       </c>
       <c r="M24">
-        <v>18.343545</v>
+        <v>19.1773425</v>
       </c>
       <c r="N24">
-        <v>136.6231216666667</v>
+        <v>135.7893241666667</v>
       </c>
       <c r="O24">
-        <v>20.49346825</v>
+        <v>20.368398625</v>
       </c>
       <c r="P24">
-        <v>116.1296534166667</v>
+        <v>115.4209255416667</v>
       </c>
       <c r="Q24">
-        <v>116.3296534166666</v>
+        <v>115.6209255416667</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.07491522122664125</v>
+        <v>0.07524759122949712</v>
       </c>
       <c r="T24">
-        <v>0.5523049879295303</v>
+        <v>0.5586099240653917</v>
       </c>
       <c r="U24">
         <v>0.0535</v>
@@ -3281,7 +3281,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>8.448021724626656</v>
+        <v>8.080716432251583</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3289,22 +3289,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.06839989524671278</v>
+        <v>0.06836141793664539</v>
       </c>
       <c r="C25">
-        <v>1345.316811752474</v>
+        <v>1331.05234461235</v>
       </c>
       <c r="D25">
-        <v>1659.271811752474</v>
+        <v>1660.59234461235</v>
       </c>
       <c r="E25">
-        <v>-661.145</v>
+        <v>-645.5599999999999</v>
       </c>
       <c r="F25">
-        <v>358.455</v>
+        <v>374.04</v>
       </c>
       <c r="G25">
         <v>44.5</v>
@@ -3325,28 +3325,28 @@
         <v>154.9666666666667</v>
       </c>
       <c r="M25">
-        <v>19.1773425</v>
+        <v>20.01114</v>
       </c>
       <c r="N25">
-        <v>135.7893241666667</v>
+        <v>134.9555266666667</v>
       </c>
       <c r="O25">
-        <v>20.368398625</v>
+        <v>20.243329</v>
       </c>
       <c r="P25">
-        <v>115.4209255416667</v>
+        <v>114.7121976666667</v>
       </c>
       <c r="Q25">
-        <v>115.6209255416667</v>
+        <v>114.9121976666666</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.07524759122949712</v>
+        <v>0.07558870781137551</v>
       </c>
       <c r="T25">
-        <v>0.5586099240653917</v>
+        <v>0.5650807795732494</v>
       </c>
       <c r="U25">
         <v>0.0535</v>
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>8.080716432251583</v>
+        <v>7.7440199142411</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3371,22 +3371,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.06836141793664539</v>
+        <v>0.06849294062657799</v>
       </c>
       <c r="C26">
-        <v>1331.05234461235</v>
+        <v>1310.962178056186</v>
       </c>
       <c r="D26">
-        <v>1660.59234461235</v>
+        <v>1656.087178056186</v>
       </c>
       <c r="E26">
-        <v>-645.5600000000001</v>
+        <v>-629.975</v>
       </c>
       <c r="F26">
-        <v>374.04</v>
+        <v>389.625</v>
       </c>
       <c r="G26">
         <v>44.5</v>
@@ -3407,45 +3407,45 @@
         <v>154.9666666666667</v>
       </c>
       <c r="M26">
-        <v>20.01114</v>
+        <v>21.1566375</v>
       </c>
       <c r="N26">
-        <v>134.9555266666667</v>
+        <v>133.8100291666667</v>
       </c>
       <c r="O26">
-        <v>20.243329</v>
+        <v>20.071504375</v>
       </c>
       <c r="P26">
-        <v>114.7121976666667</v>
+        <v>113.7385247916667</v>
       </c>
       <c r="Q26">
-        <v>114.9121976666667</v>
+        <v>113.9385247916667</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.07558870781137551</v>
+        <v>0.07593892083543732</v>
       </c>
       <c r="T26">
-        <v>0.5650807795732494</v>
+        <v>0.5717241912279832</v>
       </c>
       <c r="U26">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V26">
         <v>0.15</v>
       </c>
       <c r="W26">
-        <v>0.04547499999999999</v>
+        <v>0.046155</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y26">
-        <v>7.744019914241103</v>
+        <v>7.324730438221418</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3453,22 +3453,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.06849294062657799</v>
+        <v>0.0684612633165106</v>
       </c>
       <c r="C27">
-        <v>1310.962178056186</v>
+        <v>1296.46001359073</v>
       </c>
       <c r="D27">
-        <v>1656.087178056186</v>
+        <v>1657.17001359073</v>
       </c>
       <c r="E27">
-        <v>-629.975</v>
+        <v>-614.39</v>
       </c>
       <c r="F27">
-        <v>389.625</v>
+        <v>405.21</v>
       </c>
       <c r="G27">
         <v>44.5</v>
@@ -3489,28 +3489,28 @@
         <v>154.9666666666667</v>
       </c>
       <c r="M27">
-        <v>21.1566375</v>
+        <v>22.002903</v>
       </c>
       <c r="N27">
-        <v>133.8100291666667</v>
+        <v>132.9637636666667</v>
       </c>
       <c r="O27">
-        <v>20.071504375</v>
+        <v>19.94456455</v>
       </c>
       <c r="P27">
-        <v>113.7385247916667</v>
+        <v>113.0191991166667</v>
       </c>
       <c r="Q27">
-        <v>113.9385247916667</v>
+        <v>113.2191991166667</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.07593892083543732</v>
+        <v>0.07629859907636569</v>
       </c>
       <c r="T27">
-        <v>0.5717241912279832</v>
+        <v>0.5785471545490614</v>
       </c>
       <c r="U27">
         <v>0.0543</v>
@@ -3527,7 +3527,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>7.324730438221418</v>
+        <v>7.043010036751362</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3535,22 +3535,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.0684612633165106</v>
+        <v>0.06842958600644322</v>
       </c>
       <c r="C28">
-        <v>1296.46001359073</v>
+        <v>1281.959266079617</v>
       </c>
       <c r="D28">
-        <v>1657.17001359073</v>
+        <v>1658.254266079617</v>
       </c>
       <c r="E28">
-        <v>-614.39</v>
+        <v>-598.8050000000001</v>
       </c>
       <c r="F28">
-        <v>405.21</v>
+        <v>420.795</v>
       </c>
       <c r="G28">
         <v>44.5</v>
@@ -3571,28 +3571,28 @@
         <v>154.9666666666667</v>
       </c>
       <c r="M28">
-        <v>22.002903</v>
+        <v>22.8491685</v>
       </c>
       <c r="N28">
-        <v>132.9637636666667</v>
+        <v>132.1174981666667</v>
       </c>
       <c r="O28">
-        <v>19.94456455</v>
+        <v>19.817624725</v>
       </c>
       <c r="P28">
-        <v>113.0191991166667</v>
+        <v>112.2998734416667</v>
       </c>
       <c r="Q28">
-        <v>113.2191991166667</v>
+        <v>112.4998734416667</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.07629859907636569</v>
+        <v>0.07666813151567564</v>
       </c>
       <c r="T28">
-        <v>0.5785471545490614</v>
+        <v>0.5855570483720869</v>
       </c>
       <c r="U28">
         <v>0.0543</v>
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>7.043010036751362</v>
+        <v>6.782157813167979</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3617,22 +3617,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.06842958600644322</v>
+        <v>0.06839790869637581</v>
       </c>
       <c r="C29">
-        <v>1281.959266079617</v>
+        <v>1267.459938305921</v>
       </c>
       <c r="D29">
-        <v>1658.254266079617</v>
+        <v>1659.339938305921</v>
       </c>
       <c r="E29">
-        <v>-598.8050000000001</v>
+        <v>-583.22</v>
       </c>
       <c r="F29">
-        <v>420.795</v>
+        <v>436.3800000000001</v>
       </c>
       <c r="G29">
         <v>44.5</v>
@@ -3653,28 +3653,28 @@
         <v>154.9666666666667</v>
       </c>
       <c r="M29">
-        <v>22.8491685</v>
+        <v>23.695434</v>
       </c>
       <c r="N29">
-        <v>132.1174981666667</v>
+        <v>131.2712326666667</v>
       </c>
       <c r="O29">
-        <v>19.817624725</v>
+        <v>19.6906849</v>
       </c>
       <c r="P29">
-        <v>112.2998734416667</v>
+        <v>111.5805477666667</v>
       </c>
       <c r="Q29">
-        <v>112.4998734416667</v>
+        <v>111.7805477666667</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.07666813151567564</v>
+        <v>0.07704792874496641</v>
       </c>
       <c r="T29">
-        <v>0.5855570483720869</v>
+        <v>0.5927616614679742</v>
       </c>
       <c r="U29">
         <v>0.0543</v>
@@ -3691,7 +3691,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>6.782157813167979</v>
+        <v>6.539937891269122</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3699,22 +3699,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.06839790869637581</v>
+        <v>0.06836623138630842</v>
       </c>
       <c r="C30">
-        <v>1267.459938305921</v>
+        <v>1252.962033060007</v>
       </c>
       <c r="D30">
-        <v>1659.339938305921</v>
+        <v>1660.427033060007</v>
       </c>
       <c r="E30">
-        <v>-583.22</v>
+        <v>-567.635</v>
       </c>
       <c r="F30">
-        <v>436.3800000000001</v>
+        <v>451.965</v>
       </c>
       <c r="G30">
         <v>44.5</v>
@@ -3735,28 +3735,28 @@
         <v>154.9666666666667</v>
       </c>
       <c r="M30">
-        <v>23.695434</v>
+        <v>24.5416995</v>
       </c>
       <c r="N30">
-        <v>131.2712326666667</v>
+        <v>130.4249671666667</v>
       </c>
       <c r="O30">
-        <v>19.6906849</v>
+        <v>19.563745075</v>
       </c>
       <c r="P30">
-        <v>111.5805477666667</v>
+        <v>110.8612220916667</v>
       </c>
       <c r="Q30">
-        <v>111.7805477666667</v>
+        <v>111.0612220916667</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.07704792874496641</v>
+        <v>0.07743842448775834</v>
       </c>
       <c r="T30">
-        <v>0.5927616614679742</v>
+        <v>0.6001692214116328</v>
       </c>
       <c r="U30">
         <v>0.0543</v>
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>6.539937891269122</v>
+        <v>6.314422791570187</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3781,22 +3781,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.06836623138630842</v>
+        <v>0.06858955407624102</v>
       </c>
       <c r="C31">
-        <v>1252.962033060007</v>
+        <v>1229.743332144119</v>
       </c>
       <c r="D31">
-        <v>1660.427033060007</v>
+        <v>1652.793332144119</v>
       </c>
       <c r="E31">
-        <v>-567.635</v>
+        <v>-552.0500000000001</v>
       </c>
       <c r="F31">
-        <v>451.965</v>
+        <v>467.55</v>
       </c>
       <c r="G31">
         <v>44.5</v>
@@ -3817,45 +3817,45 @@
         <v>154.9666666666667</v>
       </c>
       <c r="M31">
-        <v>24.5416995</v>
+        <v>25.855515</v>
       </c>
       <c r="N31">
-        <v>130.4249671666667</v>
+        <v>129.1111516666667</v>
       </c>
       <c r="O31">
-        <v>19.563745075</v>
+        <v>19.36667275</v>
       </c>
       <c r="P31">
-        <v>110.8612220916667</v>
+        <v>109.7444789166667</v>
       </c>
       <c r="Q31">
-        <v>111.0612220916667</v>
+        <v>109.9444789166667</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.07743842448775834</v>
+        <v>0.07784007725177289</v>
       </c>
       <c r="T31">
-        <v>0.6001692214116328</v>
+        <v>0.6077884259251103</v>
       </c>
       <c r="U31">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V31">
         <v>0.15</v>
       </c>
       <c r="W31">
-        <v>0.046155</v>
+        <v>0.047005</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y31">
-        <v>6.314422791570188</v>
+        <v>5.993563333264361</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3863,22 +3863,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.06858955407624102</v>
+        <v>0.06856637676617364</v>
       </c>
       <c r="C32">
-        <v>1229.743332144119</v>
+        <v>1214.947321867074</v>
       </c>
       <c r="D32">
-        <v>1652.793332144119</v>
+        <v>1653.582321867074</v>
       </c>
       <c r="E32">
-        <v>-552.0500000000001</v>
+        <v>-536.465</v>
       </c>
       <c r="F32">
-        <v>467.55</v>
+        <v>483.135</v>
       </c>
       <c r="G32">
         <v>44.5</v>
@@ -3899,28 +3899,28 @@
         <v>154.9666666666667</v>
       </c>
       <c r="M32">
-        <v>25.855515</v>
+        <v>26.7173655</v>
       </c>
       <c r="N32">
-        <v>129.1111516666667</v>
+        <v>128.2493011666667</v>
       </c>
       <c r="O32">
-        <v>19.36667275</v>
+        <v>19.237395175</v>
       </c>
       <c r="P32">
-        <v>109.7444789166667</v>
+        <v>109.0119059916667</v>
       </c>
       <c r="Q32">
-        <v>109.9444789166667</v>
+        <v>109.2119059916667</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.07784007725177289</v>
+        <v>0.07825337212488934</v>
       </c>
       <c r="T32">
-        <v>0.6077884259251103</v>
+        <v>0.6156284769462249</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -3937,7 +3937,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>5.993563333264361</v>
+        <v>5.800222580578414</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3945,22 +3945,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.06856637676617364</v>
+        <v>0.06854319945610624</v>
       </c>
       <c r="C33">
-        <v>1214.947321867074</v>
+        <v>1200.1520652258</v>
       </c>
       <c r="D33">
-        <v>1653.582321867074</v>
+        <v>1654.3720652258</v>
       </c>
       <c r="E33">
-        <v>-536.465</v>
+        <v>-520.88</v>
       </c>
       <c r="F33">
-        <v>483.135</v>
+        <v>498.72</v>
       </c>
       <c r="G33">
         <v>44.5</v>
@@ -3981,28 +3981,28 @@
         <v>154.9666666666667</v>
       </c>
       <c r="M33">
-        <v>26.7173655</v>
+        <v>27.579216</v>
       </c>
       <c r="N33">
-        <v>128.2493011666667</v>
+        <v>127.3874506666667</v>
       </c>
       <c r="O33">
-        <v>19.237395175</v>
+        <v>19.1081176</v>
       </c>
       <c r="P33">
-        <v>109.0119059916667</v>
+        <v>108.2793330666667</v>
       </c>
       <c r="Q33">
-        <v>109.2119059916667</v>
+        <v>108.4793330666667</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.07825337212488934</v>
+        <v>0.078678822729568</v>
       </c>
       <c r="T33">
-        <v>0.6156284769462249</v>
+        <v>0.6236991177032545</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.800222580578414</v>
+        <v>5.618965624935337</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4027,22 +4027,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.06854319945610624</v>
+        <v>0.06852002214603883</v>
       </c>
       <c r="C34">
-        <v>1200.1520652258</v>
+        <v>1185.357563300612</v>
       </c>
       <c r="D34">
-        <v>1654.3720652258</v>
+        <v>1655.162563300612</v>
       </c>
       <c r="E34">
-        <v>-520.88</v>
+        <v>-505.295</v>
       </c>
       <c r="F34">
-        <v>498.72</v>
+        <v>514.3050000000001</v>
       </c>
       <c r="G34">
         <v>44.5</v>
@@ -4063,28 +4063,28 @@
         <v>154.9666666666667</v>
       </c>
       <c r="M34">
-        <v>27.579216</v>
+        <v>28.44106650000001</v>
       </c>
       <c r="N34">
-        <v>127.3874506666667</v>
+        <v>126.5256001666667</v>
       </c>
       <c r="O34">
-        <v>19.1081176</v>
+        <v>18.978840025</v>
       </c>
       <c r="P34">
-        <v>108.2793330666667</v>
+        <v>107.5467601416667</v>
       </c>
       <c r="Q34">
-        <v>108.4793330666667</v>
+        <v>107.7467601416667</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.078678822729568</v>
+        <v>0.07911697335229678</v>
       </c>
       <c r="T34">
-        <v>0.6236991177032545</v>
+        <v>0.6320106731097478</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4101,7 +4101,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.618965624935337</v>
+        <v>5.448693939331235</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.06852002214603883</v>
+        <v>0.06849684483597143</v>
       </c>
       <c r="C35">
-        <v>1185.357563300612</v>
+        <v>1170.563817173891</v>
       </c>
       <c r="D35">
-        <v>1655.162563300612</v>
+        <v>1655.95381717389</v>
       </c>
       <c r="E35">
-        <v>-505.295</v>
+        <v>-489.71</v>
       </c>
       <c r="F35">
-        <v>514.3050000000001</v>
+        <v>529.89</v>
       </c>
       <c r="G35">
         <v>44.5</v>
@@ -4145,28 +4145,28 @@
         <v>154.9666666666667</v>
       </c>
       <c r="M35">
-        <v>28.44106650000001</v>
+        <v>29.302917</v>
       </c>
       <c r="N35">
-        <v>126.5256001666667</v>
+        <v>125.6637496666667</v>
       </c>
       <c r="O35">
-        <v>18.978840025</v>
+        <v>18.84956245</v>
       </c>
       <c r="P35">
-        <v>107.5467601416667</v>
+        <v>106.8141872166667</v>
       </c>
       <c r="Q35">
-        <v>107.7467601416667</v>
+        <v>107.0141872166667</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.07911697335229678</v>
+        <v>0.0795684012666234</v>
       </c>
       <c r="T35">
-        <v>0.6320106731097478</v>
+        <v>0.6405740938315894</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4183,7 +4183,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.448693939331235</v>
+        <v>5.288438235233259</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4191,22 +4191,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.06849684483597143</v>
+        <v>0.06847366752590406</v>
       </c>
       <c r="C36">
-        <v>1170.563817173891</v>
+        <v>1155.770827930086</v>
       </c>
       <c r="D36">
-        <v>1655.95381717389</v>
+        <v>1656.745827930086</v>
       </c>
       <c r="E36">
-        <v>-489.71</v>
+        <v>-474.125</v>
       </c>
       <c r="F36">
-        <v>529.89</v>
+        <v>545.475</v>
       </c>
       <c r="G36">
         <v>44.5</v>
@@ -4227,28 +4227,28 @@
         <v>154.9666666666667</v>
       </c>
       <c r="M36">
-        <v>29.302917</v>
+        <v>30.1647675</v>
       </c>
       <c r="N36">
-        <v>125.6637496666667</v>
+        <v>124.8018991666667</v>
       </c>
       <c r="O36">
-        <v>18.84956245</v>
+        <v>18.720284875</v>
       </c>
       <c r="P36">
-        <v>106.8141872166667</v>
+        <v>106.0816142916667</v>
       </c>
       <c r="Q36">
-        <v>107.0141872166667</v>
+        <v>106.2816142916666</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.0795684012666234</v>
+        <v>0.08003371927062163</v>
       </c>
       <c r="T36">
-        <v>0.6405740938315894</v>
+        <v>0.6494010044217953</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4265,7 +4265,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.288438235233259</v>
+        <v>5.137339999940879</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4273,22 +4273,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.06847366752590406</v>
+        <v>0.06845049021583666</v>
       </c>
       <c r="C37">
-        <v>1155.770827930086</v>
+        <v>1140.978596655727</v>
       </c>
       <c r="D37">
-        <v>1656.745827930086</v>
+        <v>1657.538596655727</v>
       </c>
       <c r="E37">
-        <v>-474.125</v>
+        <v>-458.54</v>
       </c>
       <c r="F37">
-        <v>545.475</v>
+        <v>561.0600000000001</v>
       </c>
       <c r="G37">
         <v>44.5</v>
@@ -4309,28 +4309,28 @@
         <v>154.9666666666667</v>
       </c>
       <c r="M37">
-        <v>30.1647675</v>
+        <v>31.026618</v>
       </c>
       <c r="N37">
-        <v>124.8018991666667</v>
+        <v>123.9400486666667</v>
       </c>
       <c r="O37">
-        <v>18.720284875</v>
+        <v>18.5910073</v>
       </c>
       <c r="P37">
-        <v>106.0816142916667</v>
+        <v>105.3490413666667</v>
       </c>
       <c r="Q37">
-        <v>106.2816142916666</v>
+        <v>105.5490413666667</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.08003371927062163</v>
+        <v>0.08051357846224479</v>
       </c>
       <c r="T37">
-        <v>0.6494010044217953</v>
+        <v>0.6585037559679451</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.137339999940879</v>
+        <v>4.994636111053634</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4355,22 +4355,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.06845049021583666</v>
+        <v>0.06842731290576927</v>
       </c>
       <c r="C38">
-        <v>1140.978596655727</v>
+        <v>1126.187124439421</v>
       </c>
       <c r="D38">
-        <v>1657.538596655727</v>
+        <v>1658.332124439421</v>
       </c>
       <c r="E38">
-        <v>-458.5400000000001</v>
+        <v>-442.955</v>
       </c>
       <c r="F38">
-        <v>561.0599999999999</v>
+        <v>576.645</v>
       </c>
       <c r="G38">
         <v>44.5</v>
@@ -4391,28 +4391,28 @@
         <v>154.9666666666667</v>
       </c>
       <c r="M38">
-        <v>31.026618</v>
+        <v>31.8884685</v>
       </c>
       <c r="N38">
-        <v>123.9400486666667</v>
+        <v>123.0781981666667</v>
       </c>
       <c r="O38">
-        <v>18.5910073</v>
+        <v>18.461729725</v>
       </c>
       <c r="P38">
-        <v>105.3490413666667</v>
+        <v>104.6164684416667</v>
       </c>
       <c r="Q38">
-        <v>105.5490413666667</v>
+        <v>104.8164684416667</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.08051357846224479</v>
+        <v>0.08100867127899884</v>
       </c>
       <c r="T38">
-        <v>0.6585037559679451</v>
+        <v>0.6678954837536553</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4429,7 +4429,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>4.994636111053634</v>
+        <v>4.859645945890022</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4437,22 +4437,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.06842731290576927</v>
+        <v>0.06840413559570188</v>
       </c>
       <c r="C39">
-        <v>1126.187124439421</v>
+        <v>1111.396412371861</v>
       </c>
       <c r="D39">
-        <v>1658.332124439421</v>
+        <v>1659.126412371861</v>
       </c>
       <c r="E39">
-        <v>-442.955</v>
+        <v>-427.37</v>
       </c>
       <c r="F39">
-        <v>576.645</v>
+        <v>592.23</v>
       </c>
       <c r="G39">
         <v>44.5</v>
@@ -4473,28 +4473,28 @@
         <v>154.9666666666667</v>
       </c>
       <c r="M39">
-        <v>31.8884685</v>
+        <v>32.750319</v>
       </c>
       <c r="N39">
-        <v>123.0781981666667</v>
+        <v>122.2163476666667</v>
       </c>
       <c r="O39">
-        <v>18.461729725</v>
+        <v>18.33245215</v>
       </c>
       <c r="P39">
-        <v>104.6164684416667</v>
+        <v>103.8838955166667</v>
       </c>
       <c r="Q39">
-        <v>104.8164684416667</v>
+        <v>104.0838955166667</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.08100867127899884</v>
+        <v>0.08151973483177721</v>
       </c>
       <c r="T39">
-        <v>0.6678954837536553</v>
+        <v>0.6775901705001948</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>4.859645945890022</v>
+        <v>4.731760526261336</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4519,22 +4519,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.06840413559570188</v>
+        <v>0.06838095828563448</v>
       </c>
       <c r="C40">
-        <v>1111.396412371861</v>
+        <v>1096.606461545831</v>
       </c>
       <c r="D40">
-        <v>1659.126412371861</v>
+        <v>1659.921461545831</v>
       </c>
       <c r="E40">
-        <v>-427.37</v>
+        <v>-411.785</v>
       </c>
       <c r="F40">
-        <v>592.23</v>
+        <v>607.8150000000001</v>
       </c>
       <c r="G40">
         <v>44.5</v>
@@ -4555,28 +4555,28 @@
         <v>154.9666666666667</v>
       </c>
       <c r="M40">
-        <v>32.750319</v>
+        <v>33.61216950000001</v>
       </c>
       <c r="N40">
-        <v>122.2163476666667</v>
+        <v>121.3544971666667</v>
       </c>
       <c r="O40">
-        <v>18.33245215</v>
+        <v>18.203174575</v>
       </c>
       <c r="P40">
-        <v>103.8838955166667</v>
+        <v>103.1513225916667</v>
       </c>
       <c r="Q40">
-        <v>104.0838955166667</v>
+        <v>103.3513225916666</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.08151973483177721</v>
+        <v>0.08204755456661389</v>
       </c>
       <c r="T40">
-        <v>0.6775901705001948</v>
+        <v>0.6876027158285879</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4593,7 +4593,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>4.731760526261336</v>
+        <v>4.610433333280277</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4601,22 +4601,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.06838095828563448</v>
+        <v>0.0692077809755671</v>
       </c>
       <c r="C41">
-        <v>1096.606461545831</v>
+        <v>1053.122375413421</v>
       </c>
       <c r="D41">
-        <v>1659.921461545831</v>
+        <v>1632.022375413421</v>
       </c>
       <c r="E41">
-        <v>-411.785</v>
+        <v>-396.1999999999999</v>
       </c>
       <c r="F41">
-        <v>607.8150000000001</v>
+        <v>623.4000000000001</v>
       </c>
       <c r="G41">
         <v>44.5</v>
@@ -4637,45 +4637,45 @@
         <v>154.9666666666667</v>
       </c>
       <c r="M41">
-        <v>33.61216950000001</v>
+        <v>36.03252000000001</v>
       </c>
       <c r="N41">
-        <v>121.3544971666667</v>
+        <v>118.9341466666667</v>
       </c>
       <c r="O41">
-        <v>18.203174575</v>
+        <v>17.840122</v>
       </c>
       <c r="P41">
-        <v>103.1513225916667</v>
+        <v>101.0940246666667</v>
       </c>
       <c r="Q41">
-        <v>103.3513225916666</v>
+        <v>101.2940246666667</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.08204755456661389</v>
+        <v>0.08259296829261181</v>
       </c>
       <c r="T41">
-        <v>0.6876027158285879</v>
+        <v>0.6979490126679277</v>
       </c>
       <c r="U41">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V41">
         <v>0.15</v>
       </c>
       <c r="W41">
-        <v>0.047005</v>
+        <v>0.04913</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y41">
-        <v>4.610433333280277</v>
+        <v>4.300744623652929</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4683,22 +4683,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.0692077809755671</v>
+        <v>0.06920585366549969</v>
       </c>
       <c r="C42">
-        <v>1053.122375413421</v>
+        <v>1037.601317199799</v>
       </c>
       <c r="D42">
-        <v>1632.022375413421</v>
+        <v>1632.086317199799</v>
       </c>
       <c r="E42">
-        <v>-396.1999999999999</v>
+        <v>-380.615</v>
       </c>
       <c r="F42">
-        <v>623.4000000000001</v>
+        <v>638.985</v>
       </c>
       <c r="G42">
         <v>44.5</v>
@@ -4719,28 +4719,28 @@
         <v>154.9666666666667</v>
       </c>
       <c r="M42">
-        <v>36.03252000000001</v>
+        <v>36.933333</v>
       </c>
       <c r="N42">
-        <v>118.9341466666667</v>
+        <v>118.0333336666667</v>
       </c>
       <c r="O42">
-        <v>17.840122</v>
+        <v>17.70500005</v>
       </c>
       <c r="P42">
-        <v>101.0940246666667</v>
+        <v>100.3283336166667</v>
       </c>
       <c r="Q42">
-        <v>101.2940246666667</v>
+        <v>100.5283336166667</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.08259296829261181</v>
+        <v>0.08315687061949101</v>
       </c>
       <c r="T42">
-        <v>0.6979490126679277</v>
+        <v>0.7086460314340247</v>
       </c>
       <c r="U42">
         <v>0.0578</v>
@@ -4757,7 +4757,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>4.300744623652929</v>
+        <v>4.195848413319931</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4765,22 +4765,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.06920585366549969</v>
+        <v>0.06920392635543229</v>
       </c>
       <c r="C43">
-        <v>1037.601317199799</v>
+        <v>1022.080263996786</v>
       </c>
       <c r="D43">
-        <v>1632.086317199799</v>
+        <v>1632.150263996786</v>
       </c>
       <c r="E43">
-        <v>-380.615</v>
+        <v>-365.03</v>
       </c>
       <c r="F43">
-        <v>638.985</v>
+        <v>654.5700000000001</v>
       </c>
       <c r="G43">
         <v>44.5</v>
@@ -4801,28 +4801,28 @@
         <v>154.9666666666667</v>
       </c>
       <c r="M43">
-        <v>36.933333</v>
+        <v>37.834146</v>
       </c>
       <c r="N43">
-        <v>118.0333336666667</v>
+        <v>117.1325206666667</v>
       </c>
       <c r="O43">
-        <v>17.70500005</v>
+        <v>17.5698781</v>
       </c>
       <c r="P43">
-        <v>100.3283336166667</v>
+        <v>99.56264256666667</v>
       </c>
       <c r="Q43">
-        <v>100.5283336166667</v>
+        <v>99.76264256666666</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.08315687061949101</v>
+        <v>0.08374021785419361</v>
       </c>
       <c r="T43">
-        <v>0.7086460314340247</v>
+        <v>0.719711912916194</v>
       </c>
       <c r="U43">
         <v>0.0578</v>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>4.195848413319931</v>
+        <v>4.095947260621838</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4847,22 +4847,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.06920392635543229</v>
+        <v>0.06920199904536491</v>
       </c>
       <c r="C44">
-        <v>1022.080263996786</v>
+        <v>1006.55921580497</v>
       </c>
       <c r="D44">
-        <v>1632.150263996786</v>
+        <v>1632.21421580497</v>
       </c>
       <c r="E44">
-        <v>-365.0300000000001</v>
+        <v>-349.4450000000001</v>
       </c>
       <c r="F44">
-        <v>654.5699999999999</v>
+        <v>670.155</v>
       </c>
       <c r="G44">
         <v>44.5</v>
@@ -4883,28 +4883,28 @@
         <v>154.9666666666667</v>
       </c>
       <c r="M44">
-        <v>37.834146</v>
+        <v>38.734959</v>
       </c>
       <c r="N44">
-        <v>117.1325206666667</v>
+        <v>116.2317076666667</v>
       </c>
       <c r="O44">
-        <v>17.5698781</v>
+        <v>17.43475615</v>
       </c>
       <c r="P44">
-        <v>99.56264256666667</v>
+        <v>98.79695151666667</v>
       </c>
       <c r="Q44">
-        <v>99.76264256666666</v>
+        <v>98.99695151666666</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.08374021785419361</v>
+        <v>0.08434403341292088</v>
       </c>
       <c r="T44">
-        <v>0.7197119129161939</v>
+        <v>0.7311660709415972</v>
       </c>
       <c r="U44">
         <v>0.0578</v>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>4.095947260621838</v>
+        <v>4.000692673165515</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4929,22 +4929,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.06920199904536491</v>
+        <v>0.07050907173529751</v>
       </c>
       <c r="C45">
-        <v>1006.55921580497</v>
+        <v>948.724075921632</v>
       </c>
       <c r="D45">
-        <v>1632.21421580497</v>
+        <v>1589.964075921632</v>
       </c>
       <c r="E45">
-        <v>-349.4450000000001</v>
+        <v>-333.86</v>
       </c>
       <c r="F45">
-        <v>670.155</v>
+        <v>685.74</v>
       </c>
       <c r="G45">
         <v>44.5</v>
@@ -4965,45 +4965,45 @@
         <v>154.9666666666667</v>
       </c>
       <c r="M45">
-        <v>38.734959</v>
+        <v>42.035862</v>
       </c>
       <c r="N45">
-        <v>116.2317076666667</v>
+        <v>112.9308046666667</v>
       </c>
       <c r="O45">
-        <v>17.43475615</v>
+        <v>16.9396207</v>
       </c>
       <c r="P45">
-        <v>98.79695151666667</v>
+        <v>95.99118396666665</v>
       </c>
       <c r="Q45">
-        <v>98.99695151666666</v>
+        <v>96.19118396666664</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.08434403341292088</v>
+        <v>0.08496941381303126</v>
       </c>
       <c r="T45">
-        <v>0.7311660709415972</v>
+        <v>0.7430293060393364</v>
       </c>
       <c r="U45">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V45">
         <v>0.15</v>
       </c>
       <c r="W45">
-        <v>0.04913</v>
+        <v>0.052105</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y45">
-        <v>4.000692673165515</v>
+        <v>3.686534765640506</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5011,22 +5011,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.07050907173529751</v>
+        <v>0.07053689442523012</v>
       </c>
       <c r="C46">
-        <v>948.724075921632</v>
+        <v>932.2634906400194</v>
       </c>
       <c r="D46">
-        <v>1589.964075921632</v>
+        <v>1589.088490640019</v>
       </c>
       <c r="E46">
-        <v>-333.86</v>
+        <v>-318.275</v>
       </c>
       <c r="F46">
-        <v>685.74</v>
+        <v>701.325</v>
       </c>
       <c r="G46">
         <v>44.5</v>
@@ -5047,28 +5047,28 @@
         <v>154.9666666666667</v>
       </c>
       <c r="M46">
-        <v>42.035862</v>
+        <v>42.99122250000001</v>
       </c>
       <c r="N46">
-        <v>112.9308046666667</v>
+        <v>111.9754441666667</v>
       </c>
       <c r="O46">
-        <v>16.9396207</v>
+        <v>16.796316625</v>
       </c>
       <c r="P46">
-        <v>95.99118396666665</v>
+        <v>95.17912754166666</v>
       </c>
       <c r="Q46">
-        <v>96.19118396666664</v>
+        <v>95.37912754166665</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.08496941381303126</v>
+        <v>0.0856175353186002</v>
       </c>
       <c r="T46">
-        <v>0.7430293060393364</v>
+        <v>0.755323931504266</v>
       </c>
       <c r="U46">
         <v>0.0613</v>
@@ -5085,7 +5085,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>3.686534765640506</v>
+        <v>3.604611770848495</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5093,22 +5093,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.07053689442523012</v>
+        <v>0.07056471711516273</v>
       </c>
       <c r="C47">
-        <v>932.2634906400194</v>
+        <v>915.8038691885201</v>
       </c>
       <c r="D47">
-        <v>1589.088490640019</v>
+        <v>1588.21386918852</v>
       </c>
       <c r="E47">
-        <v>-318.275</v>
+        <v>-302.6899999999999</v>
       </c>
       <c r="F47">
-        <v>701.325</v>
+        <v>716.9100000000001</v>
       </c>
       <c r="G47">
         <v>44.5</v>
@@ -5129,28 +5129,28 @@
         <v>154.9666666666667</v>
       </c>
       <c r="M47">
-        <v>42.99122250000001</v>
+        <v>43.946583</v>
       </c>
       <c r="N47">
-        <v>111.9754441666667</v>
+        <v>111.0200836666667</v>
       </c>
       <c r="O47">
-        <v>16.796316625</v>
+        <v>16.65301255</v>
       </c>
       <c r="P47">
-        <v>95.17912754166666</v>
+        <v>94.36707111666666</v>
       </c>
       <c r="Q47">
-        <v>95.37912754166665</v>
+        <v>94.56707111666665</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.0856175353186002</v>
+        <v>0.08628966132437541</v>
       </c>
       <c r="T47">
-        <v>0.755323931504266</v>
+        <v>0.7680739134678968</v>
       </c>
       <c r="U47">
         <v>0.0613</v>
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.604611770848495</v>
+        <v>3.526250645395267</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.07056471711516273</v>
+        <v>0.07171113980509533</v>
       </c>
       <c r="C48">
-        <v>915.8038691885201</v>
+        <v>864.9990206857298</v>
       </c>
       <c r="D48">
-        <v>1588.21386918852</v>
+        <v>1552.99402068573</v>
       </c>
       <c r="E48">
-        <v>-302.6899999999999</v>
+        <v>-287.105</v>
       </c>
       <c r="F48">
-        <v>716.9100000000001</v>
+        <v>732.495</v>
       </c>
       <c r="G48">
         <v>44.5</v>
@@ -5211,45 +5211,45 @@
         <v>154.9666666666667</v>
       </c>
       <c r="M48">
-        <v>43.946583</v>
+        <v>46.9529295</v>
       </c>
       <c r="N48">
-        <v>111.0200836666667</v>
+        <v>108.0137371666667</v>
       </c>
       <c r="O48">
-        <v>16.65301255</v>
+        <v>16.202060575</v>
       </c>
       <c r="P48">
-        <v>94.36707111666666</v>
+        <v>91.81167659166667</v>
       </c>
       <c r="Q48">
-        <v>94.56707111666665</v>
+        <v>92.01167659166666</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.08628966132437541</v>
+        <v>0.08698715057565155</v>
       </c>
       <c r="T48">
-        <v>0.7680739134678968</v>
+        <v>0.7813050268263815</v>
       </c>
       <c r="U48">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V48">
         <v>0.15</v>
       </c>
       <c r="W48">
-        <v>0.052105</v>
+        <v>0.054485</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y48">
-        <v>3.526250645395267</v>
+        <v>3.300468539809995</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5257,22 +5257,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.07171113980509533</v>
+        <v>0.07176276249502793</v>
       </c>
       <c r="C49">
-        <v>864.9990206857298</v>
+        <v>847.8648092724283</v>
       </c>
       <c r="D49">
-        <v>1552.99402068573</v>
+        <v>1551.444809272428</v>
       </c>
       <c r="E49">
-        <v>-287.105</v>
+        <v>-271.52</v>
       </c>
       <c r="F49">
-        <v>732.495</v>
+        <v>748.08</v>
       </c>
       <c r="G49">
         <v>44.5</v>
@@ -5293,28 +5293,28 @@
         <v>154.9666666666667</v>
       </c>
       <c r="M49">
-        <v>46.9529295</v>
+        <v>47.951928</v>
       </c>
       <c r="N49">
-        <v>108.0137371666667</v>
+        <v>107.0147386666667</v>
       </c>
       <c r="O49">
-        <v>16.202060575</v>
+        <v>16.0522108</v>
       </c>
       <c r="P49">
-        <v>91.81167659166667</v>
+        <v>90.96252786666666</v>
       </c>
       <c r="Q49">
-        <v>92.01167659166666</v>
+        <v>91.16252786666665</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.08698715057565155</v>
+        <v>0.08771146633659216</v>
       </c>
       <c r="T49">
-        <v>0.7813050268263815</v>
+        <v>0.7950450291601925</v>
       </c>
       <c r="U49">
         <v>0.0641</v>
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.300468539809995</v>
+        <v>3.231708778563954</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5339,22 +5339,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.07176276249502792</v>
+        <v>0.07181438518496053</v>
       </c>
       <c r="C50">
-        <v>847.8648092724286</v>
+        <v>830.73368565489</v>
       </c>
       <c r="D50">
-        <v>1551.444809272429</v>
+        <v>1549.89868565489</v>
       </c>
       <c r="E50">
-        <v>-271.5200000000001</v>
+        <v>-255.9350000000001</v>
       </c>
       <c r="F50">
-        <v>748.0799999999999</v>
+        <v>763.665</v>
       </c>
       <c r="G50">
         <v>44.5</v>
@@ -5375,28 +5375,28 @@
         <v>154.9666666666667</v>
       </c>
       <c r="M50">
-        <v>47.951928</v>
+        <v>48.9509265</v>
       </c>
       <c r="N50">
-        <v>107.0147386666667</v>
+        <v>106.0157401666667</v>
       </c>
       <c r="O50">
-        <v>16.0522108</v>
+        <v>15.902361025</v>
       </c>
       <c r="P50">
-        <v>90.96252786666668</v>
+        <v>90.11337914166666</v>
       </c>
       <c r="Q50">
-        <v>91.16252786666666</v>
+        <v>90.31337914166664</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.08771146633659216</v>
+        <v>0.08846418663717751</v>
       </c>
       <c r="T50">
-        <v>0.7950450291601925</v>
+        <v>0.8093238551149373</v>
       </c>
       <c r="U50">
         <v>0.0641</v>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>3.231708778563954</v>
+        <v>3.165755538185098</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5421,22 +5421,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.07181438518496053</v>
+        <v>0.07186600787489314</v>
       </c>
       <c r="C51">
-        <v>830.73368565489</v>
+        <v>813.60564061069</v>
       </c>
       <c r="D51">
-        <v>1549.89868565489</v>
+        <v>1548.35564061069</v>
       </c>
       <c r="E51">
-        <v>-255.9350000000001</v>
+        <v>-240.35</v>
       </c>
       <c r="F51">
-        <v>763.665</v>
+        <v>779.25</v>
       </c>
       <c r="G51">
         <v>44.5</v>
@@ -5457,28 +5457,28 @@
         <v>154.9666666666667</v>
       </c>
       <c r="M51">
-        <v>48.9509265</v>
+        <v>49.949925</v>
       </c>
       <c r="N51">
-        <v>106.0157401666667</v>
+        <v>105.0167416666667</v>
       </c>
       <c r="O51">
-        <v>15.902361025</v>
+        <v>15.75251125</v>
       </c>
       <c r="P51">
-        <v>90.11337914166666</v>
+        <v>89.26423041666666</v>
       </c>
       <c r="Q51">
-        <v>90.31337914166664</v>
+        <v>89.46423041666665</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.08846418663717751</v>
+        <v>0.08924701574978627</v>
       </c>
       <c r="T51">
-        <v>0.8093238551149373</v>
+        <v>0.824173834107872</v>
       </c>
       <c r="U51">
         <v>0.0641</v>
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.165755538185098</v>
+        <v>3.102440427421396</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5503,22 +5503,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.07186600787489314</v>
+        <v>0.07191763056482574</v>
       </c>
       <c r="C52">
-        <v>813.60564061069</v>
+        <v>796.4806649540947</v>
       </c>
       <c r="D52">
-        <v>1548.35564061069</v>
+        <v>1546.815664954095</v>
       </c>
       <c r="E52">
-        <v>-240.35</v>
+        <v>-224.765</v>
       </c>
       <c r="F52">
-        <v>779.25</v>
+        <v>794.835</v>
       </c>
       <c r="G52">
         <v>44.5</v>
@@ -5539,28 +5539,28 @@
         <v>154.9666666666667</v>
       </c>
       <c r="M52">
-        <v>49.949925</v>
+        <v>50.94892350000001</v>
       </c>
       <c r="N52">
-        <v>105.0167416666667</v>
+        <v>104.0177431666667</v>
       </c>
       <c r="O52">
-        <v>15.75251125</v>
+        <v>15.602661475</v>
       </c>
       <c r="P52">
-        <v>89.26423041666666</v>
+        <v>88.41508169166667</v>
       </c>
       <c r="Q52">
-        <v>89.46423041666665</v>
+        <v>88.61508169166666</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.08924701574978627</v>
+        <v>0.09006179707107295</v>
       </c>
       <c r="T52">
-        <v>0.824173834107872</v>
+        <v>0.839629934692355</v>
       </c>
       <c r="U52">
         <v>0.0641</v>
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.102440427421396</v>
+        <v>3.041608262177839</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5585,22 +5585,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.07191763056482574</v>
+        <v>0.07541685325475836</v>
       </c>
       <c r="C53">
-        <v>796.4806649540947</v>
+        <v>683.1993375654238</v>
       </c>
       <c r="D53">
-        <v>1546.815664954095</v>
+        <v>1449.119337565424</v>
       </c>
       <c r="E53">
-        <v>-224.765</v>
+        <v>-209.1799999999999</v>
       </c>
       <c r="F53">
-        <v>794.835</v>
+        <v>810.4200000000001</v>
       </c>
       <c r="G53">
         <v>44.5</v>
@@ -5621,45 +5621,45 @@
         <v>154.9666666666667</v>
       </c>
       <c r="M53">
-        <v>50.94892350000001</v>
+        <v>58.26919800000001</v>
       </c>
       <c r="N53">
-        <v>104.0177431666667</v>
+        <v>96.69746866666665</v>
       </c>
       <c r="O53">
-        <v>15.602661475</v>
+        <v>14.5046203</v>
       </c>
       <c r="P53">
-        <v>88.41508169166667</v>
+        <v>82.19284836666665</v>
       </c>
       <c r="Q53">
-        <v>88.61508169166666</v>
+        <v>82.39284836666664</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.09006179707107295</v>
+        <v>0.0909105276140799</v>
       </c>
       <c r="T53">
-        <v>0.839629934692355</v>
+        <v>0.8557300394678582</v>
       </c>
       <c r="U53">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V53">
         <v>0.15</v>
       </c>
       <c r="W53">
-        <v>0.054485</v>
+        <v>0.061115</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y53">
-        <v>3.041608262177839</v>
+        <v>2.659495445031981</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5667,22 +5667,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.07541685325475836</v>
+        <v>0.07553477594469096</v>
       </c>
       <c r="C54">
-        <v>683.1993375654238</v>
+        <v>664.536496231494</v>
       </c>
       <c r="D54">
-        <v>1449.119337565424</v>
+        <v>1446.041496231494</v>
       </c>
       <c r="E54">
-        <v>-209.1799999999999</v>
+        <v>-193.595</v>
       </c>
       <c r="F54">
-        <v>810.4200000000001</v>
+        <v>826.005</v>
       </c>
       <c r="G54">
         <v>44.5</v>
@@ -5703,28 +5703,28 @@
         <v>154.9666666666667</v>
       </c>
       <c r="M54">
-        <v>58.26919800000001</v>
+        <v>59.3897595</v>
       </c>
       <c r="N54">
-        <v>96.69746866666665</v>
+        <v>95.57690716666667</v>
       </c>
       <c r="O54">
-        <v>14.5046203</v>
+        <v>14.336536075</v>
       </c>
       <c r="P54">
-        <v>82.19284836666665</v>
+        <v>81.24037109166667</v>
       </c>
       <c r="Q54">
-        <v>82.39284836666664</v>
+        <v>81.44037109166666</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.0909105276140799</v>
+        <v>0.0917953743504063</v>
       </c>
       <c r="T54">
-        <v>0.8557300394678582</v>
+        <v>0.872515255084872</v>
       </c>
       <c r="U54">
         <v>0.07190000000000001</v>
@@ -5741,7 +5741,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.659495445031981</v>
+        <v>2.609316285691756</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5749,22 +5749,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.07553477594469096</v>
+        <v>0.07565269863462357</v>
       </c>
       <c r="C55">
-        <v>664.536496231494</v>
+        <v>645.8867014829926</v>
       </c>
       <c r="D55">
-        <v>1446.041496231494</v>
+        <v>1442.976701482993</v>
       </c>
       <c r="E55">
-        <v>-193.595</v>
+        <v>-178.01</v>
       </c>
       <c r="F55">
-        <v>826.005</v>
+        <v>841.59</v>
       </c>
       <c r="G55">
         <v>44.5</v>
@@ -5785,28 +5785,28 @@
         <v>154.9666666666667</v>
       </c>
       <c r="M55">
-        <v>59.3897595</v>
+        <v>60.510321</v>
       </c>
       <c r="N55">
-        <v>95.57690716666667</v>
+        <v>94.45634566666666</v>
       </c>
       <c r="O55">
-        <v>14.336536075</v>
+        <v>14.16845185</v>
       </c>
       <c r="P55">
-        <v>81.24037109166667</v>
+        <v>80.28789381666667</v>
       </c>
       <c r="Q55">
-        <v>81.44037109166666</v>
+        <v>80.48789381666666</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.0917953743504063</v>
+        <v>0.09271869268396427</v>
       </c>
       <c r="T55">
-        <v>0.872515255084872</v>
+        <v>0.8900302626852343</v>
       </c>
       <c r="U55">
         <v>0.07190000000000001</v>
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.609316285691756</v>
+        <v>2.560995613734501</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5831,22 +5831,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.07565269863462357</v>
+        <v>0.07577062132455617</v>
       </c>
       <c r="C56">
-        <v>645.8867014829926</v>
+        <v>627.2498705410925</v>
       </c>
       <c r="D56">
-        <v>1442.976701482993</v>
+        <v>1439.924870541093</v>
       </c>
       <c r="E56">
-        <v>-178.01</v>
+        <v>-162.425</v>
       </c>
       <c r="F56">
-        <v>841.59</v>
+        <v>857.1750000000001</v>
       </c>
       <c r="G56">
         <v>44.5</v>
@@ -5867,28 +5867,28 @@
         <v>154.9666666666667</v>
       </c>
       <c r="M56">
-        <v>60.510321</v>
+        <v>61.63088250000001</v>
       </c>
       <c r="N56">
-        <v>94.45634566666666</v>
+        <v>93.33578416666666</v>
       </c>
       <c r="O56">
-        <v>14.16845185</v>
+        <v>14.000367625</v>
       </c>
       <c r="P56">
-        <v>80.28789381666667</v>
+        <v>79.33541654166666</v>
       </c>
       <c r="Q56">
-        <v>80.48789381666666</v>
+        <v>79.53541654166665</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.09271869268396427</v>
+        <v>0.0936830473879026</v>
       </c>
       <c r="T56">
-        <v>0.8900302626852343</v>
+        <v>0.908323715067835</v>
       </c>
       <c r="U56">
         <v>0.07190000000000001</v>
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.560995613734501</v>
+        <v>2.514432057121146</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5913,22 +5913,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.07577062132455617</v>
+        <v>0.07774494401448878</v>
       </c>
       <c r="C57">
-        <v>627.2498705410925</v>
+        <v>562.4213008647449</v>
       </c>
       <c r="D57">
-        <v>1439.924870541093</v>
+        <v>1390.681300864745</v>
       </c>
       <c r="E57">
-        <v>-162.425</v>
+        <v>-146.8399999999999</v>
       </c>
       <c r="F57">
-        <v>857.1750000000001</v>
+        <v>872.7600000000001</v>
       </c>
       <c r="G57">
         <v>44.5</v>
@@ -5949,45 +5949,45 @@
         <v>154.9666666666667</v>
       </c>
       <c r="M57">
-        <v>61.63088250000001</v>
+        <v>66.15520800000002</v>
       </c>
       <c r="N57">
-        <v>93.33578416666666</v>
+        <v>88.81145866666665</v>
       </c>
       <c r="O57">
-        <v>14.000367625</v>
+        <v>13.3217188</v>
       </c>
       <c r="P57">
-        <v>79.33541654166666</v>
+        <v>75.48973986666665</v>
       </c>
       <c r="Q57">
-        <v>79.53541654166665</v>
+        <v>75.68973986666664</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.0936830473879026</v>
+        <v>0.0946912363965654</v>
       </c>
       <c r="T57">
-        <v>0.908323715067835</v>
+        <v>0.9274486880132812</v>
       </c>
       <c r="U57">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V57">
         <v>0.15</v>
       </c>
       <c r="W57">
-        <v>0.061115</v>
+        <v>0.06443</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y57">
-        <v>2.514432057121146</v>
+        <v>2.342471157624757</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5995,22 +5995,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.07774494401448878</v>
+        <v>0.07789601670442138</v>
       </c>
       <c r="C58">
-        <v>562.4213008647449</v>
+        <v>543.2066058123738</v>
       </c>
       <c r="D58">
-        <v>1390.681300864745</v>
+        <v>1387.051605812374</v>
       </c>
       <c r="E58">
-        <v>-146.8399999999999</v>
+        <v>-131.2549999999999</v>
       </c>
       <c r="F58">
-        <v>872.7600000000001</v>
+        <v>888.3450000000001</v>
       </c>
       <c r="G58">
         <v>44.5</v>
@@ -6031,28 +6031,28 @@
         <v>154.9666666666667</v>
       </c>
       <c r="M58">
-        <v>66.15520800000002</v>
+        <v>67.33655100000001</v>
       </c>
       <c r="N58">
-        <v>88.81145866666665</v>
+        <v>87.63011566666665</v>
       </c>
       <c r="O58">
-        <v>13.3217188</v>
+        <v>13.14451735</v>
       </c>
       <c r="P58">
-        <v>75.48973986666665</v>
+        <v>74.48559831666665</v>
       </c>
       <c r="Q58">
-        <v>75.68973986666664</v>
+        <v>74.68559831666664</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.0946912363965654</v>
+        <v>0.09574631791725903</v>
       </c>
       <c r="T58">
-        <v>0.9274486880132812</v>
+        <v>0.9474631945840969</v>
       </c>
       <c r="U58">
         <v>0.07580000000000001</v>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.342471157624757</v>
+        <v>2.30137517240327</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6077,22 +6077,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.07789601670442138</v>
+        <v>0.07804708939435398</v>
       </c>
       <c r="C59">
-        <v>543.2066058123738</v>
+        <v>524.0108085327549</v>
       </c>
       <c r="D59">
-        <v>1387.051605812374</v>
+        <v>1383.440808532755</v>
       </c>
       <c r="E59">
-        <v>-131.2549999999999</v>
+        <v>-115.67</v>
       </c>
       <c r="F59">
-        <v>888.3450000000001</v>
+        <v>903.9300000000001</v>
       </c>
       <c r="G59">
         <v>44.5</v>
@@ -6113,28 +6113,28 @@
         <v>154.9666666666667</v>
       </c>
       <c r="M59">
-        <v>67.33655100000001</v>
+        <v>68.51789400000001</v>
       </c>
       <c r="N59">
-        <v>87.63011566666665</v>
+        <v>86.44877266666666</v>
       </c>
       <c r="O59">
-        <v>13.14451735</v>
+        <v>12.9673159</v>
       </c>
       <c r="P59">
-        <v>74.48559831666665</v>
+        <v>73.48145676666665</v>
       </c>
       <c r="Q59">
-        <v>74.68559831666664</v>
+        <v>73.68145676666664</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.09574631791725903</v>
+        <v>0.09685164141512854</v>
       </c>
       <c r="T59">
-        <v>0.9474631945840969</v>
+        <v>0.96843077289638</v>
       </c>
       <c r="U59">
         <v>0.07580000000000001</v>
@@ -6151,7 +6151,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.30137517240327</v>
+        <v>2.261696290120456</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6159,22 +6159,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.07804708939435398</v>
+        <v>0.07819816208428659</v>
       </c>
       <c r="C60">
-        <v>524.010808532755</v>
+        <v>504.833761824037</v>
       </c>
       <c r="D60">
-        <v>1383.440808532755</v>
+        <v>1379.848761824037</v>
       </c>
       <c r="E60">
-        <v>-115.6700000000001</v>
+        <v>-100.085</v>
       </c>
       <c r="F60">
-        <v>903.9299999999999</v>
+        <v>919.515</v>
       </c>
       <c r="G60">
         <v>44.5</v>
@@ -6195,28 +6195,28 @@
         <v>154.9666666666667</v>
       </c>
       <c r="M60">
-        <v>68.517894</v>
+        <v>69.69923700000001</v>
       </c>
       <c r="N60">
-        <v>86.44877266666667</v>
+        <v>85.26742966666666</v>
       </c>
       <c r="O60">
-        <v>12.9673159</v>
+        <v>12.79011445</v>
       </c>
       <c r="P60">
-        <v>73.48145676666667</v>
+        <v>72.47731521666665</v>
       </c>
       <c r="Q60">
-        <v>73.68145676666666</v>
+        <v>72.67731521666664</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.09685164141512853</v>
+        <v>0.09801088313240632</v>
       </c>
       <c r="T60">
-        <v>0.9684307728963798</v>
+        <v>0.990421159906823</v>
       </c>
       <c r="U60">
         <v>0.07580000000000001</v>
@@ -6233,7 +6233,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.261696290120456</v>
+        <v>2.223362454694685</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.07819816208428659</v>
+        <v>0.07834923477421921</v>
       </c>
       <c r="C61">
-        <v>504.833761824037</v>
+        <v>485.6753200092244</v>
       </c>
       <c r="D61">
-        <v>1379.848761824037</v>
+        <v>1376.275320009224</v>
       </c>
       <c r="E61">
-        <v>-100.085</v>
+        <v>-84.50000000000011</v>
       </c>
       <c r="F61">
-        <v>919.515</v>
+        <v>935.0999999999999</v>
       </c>
       <c r="G61">
         <v>44.5</v>
@@ -6277,28 +6277,28 @@
         <v>154.9666666666667</v>
       </c>
       <c r="M61">
-        <v>69.69923700000001</v>
+        <v>70.88057999999999</v>
       </c>
       <c r="N61">
-        <v>85.26742966666666</v>
+        <v>84.08608666666667</v>
       </c>
       <c r="O61">
-        <v>12.79011445</v>
+        <v>12.612913</v>
       </c>
       <c r="P61">
-        <v>72.47731521666665</v>
+        <v>71.47317366666667</v>
       </c>
       <c r="Q61">
-        <v>72.67731521666664</v>
+        <v>71.67317366666666</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.09801088313240632</v>
+        <v>0.09922808693554799</v>
       </c>
       <c r="T61">
-        <v>0.990421159906823</v>
+        <v>1.013511066267788</v>
       </c>
       <c r="U61">
         <v>0.07580000000000001</v>
@@ -6315,7 +6315,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.223362454694685</v>
+        <v>2.186306413783108</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6323,22 +6323,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.07834923477421921</v>
+        <v>0.07850030746415179</v>
       </c>
       <c r="C62">
-        <v>485.6753200092244</v>
+        <v>466.5353389164832</v>
       </c>
       <c r="D62">
-        <v>1376.275320009224</v>
+        <v>1372.720338916483</v>
       </c>
       <c r="E62">
-        <v>-84.50000000000011</v>
+        <v>-68.91500000000008</v>
       </c>
       <c r="F62">
-        <v>935.0999999999999</v>
+        <v>950.6849999999999</v>
       </c>
       <c r="G62">
         <v>44.5</v>
@@ -6359,28 +6359,28 @@
         <v>154.9666666666667</v>
       </c>
       <c r="M62">
-        <v>70.88057999999999</v>
+        <v>72.06192300000001</v>
       </c>
       <c r="N62">
-        <v>84.08608666666667</v>
+        <v>82.90474366666666</v>
       </c>
       <c r="O62">
-        <v>12.612913</v>
+        <v>12.43571155</v>
       </c>
       <c r="P62">
-        <v>71.47317366666667</v>
+        <v>70.46903211666667</v>
       </c>
       <c r="Q62">
-        <v>71.67317366666666</v>
+        <v>70.66903211666666</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.09922808693554799</v>
+        <v>0.1005077114465431</v>
       </c>
       <c r="T62">
-        <v>1.013511066267788</v>
+        <v>1.037785070390855</v>
       </c>
       <c r="U62">
         <v>0.07580000000000001</v>
@@ -6397,7 +6397,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.186306413783108</v>
+        <v>2.150465325032565</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6405,22 +6405,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.07850030746415179</v>
+        <v>0.0786513801540844</v>
       </c>
       <c r="C63">
-        <v>466.5353389164832</v>
+        <v>447.4136758597485</v>
       </c>
       <c r="D63">
-        <v>1372.720338916483</v>
+        <v>1369.183675859749</v>
       </c>
       <c r="E63">
-        <v>-68.91500000000008</v>
+        <v>-53.33000000000004</v>
       </c>
       <c r="F63">
-        <v>950.6849999999999</v>
+        <v>966.27</v>
       </c>
       <c r="G63">
         <v>44.5</v>
@@ -6441,28 +6441,28 @@
         <v>154.9666666666667</v>
       </c>
       <c r="M63">
-        <v>72.06192300000001</v>
+        <v>73.24326600000001</v>
       </c>
       <c r="N63">
-        <v>82.90474366666666</v>
+        <v>81.72340066666666</v>
       </c>
       <c r="O63">
-        <v>12.43571155</v>
+        <v>12.2585101</v>
       </c>
       <c r="P63">
-        <v>70.46903211666667</v>
+        <v>69.46489056666667</v>
       </c>
       <c r="Q63">
-        <v>70.66903211666666</v>
+        <v>69.66489056666666</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1005077114465431</v>
+        <v>0.1018546846160116</v>
       </c>
       <c r="T63">
-        <v>1.037785070390855</v>
+        <v>1.063336653678293</v>
       </c>
       <c r="U63">
         <v>0.07580000000000001</v>
@@ -6479,7 +6479,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.150465325032565</v>
+        <v>2.115780400435265</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6487,22 +6487,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.0786513801540844</v>
+        <v>0.07880245284401702</v>
       </c>
       <c r="C64">
-        <v>447.4136758597485</v>
+        <v>428.3101896196388</v>
       </c>
       <c r="D64">
-        <v>1369.183675859749</v>
+        <v>1365.665189619639</v>
       </c>
       <c r="E64">
-        <v>-53.33000000000004</v>
+        <v>-37.745</v>
       </c>
       <c r="F64">
-        <v>966.27</v>
+        <v>981.855</v>
       </c>
       <c r="G64">
         <v>44.5</v>
@@ -6523,28 +6523,28 @@
         <v>154.9666666666667</v>
       </c>
       <c r="M64">
-        <v>73.24326600000001</v>
+        <v>74.424609</v>
       </c>
       <c r="N64">
-        <v>81.72340066666666</v>
+        <v>80.54205766666666</v>
       </c>
       <c r="O64">
-        <v>12.2585101</v>
+        <v>12.08130865</v>
       </c>
       <c r="P64">
-        <v>69.46489056666667</v>
+        <v>68.46074901666667</v>
       </c>
       <c r="Q64">
-        <v>69.66489056666666</v>
+        <v>68.66074901666666</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1018546846160116</v>
+        <v>0.1032744671459919</v>
       </c>
       <c r="T64">
-        <v>1.063336653678293</v>
+        <v>1.090269403629917</v>
       </c>
       <c r="U64">
         <v>0.07580000000000001</v>
@@ -6561,7 +6561,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.115780400435265</v>
+        <v>2.082196584555341</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6569,22 +6569,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.07880245284401702</v>
+        <v>0.07895352553394963</v>
       </c>
       <c r="C65">
-        <v>428.3101896196388</v>
+        <v>409.2247404246559</v>
       </c>
       <c r="D65">
-        <v>1365.665189619639</v>
+        <v>1362.164740424656</v>
       </c>
       <c r="E65">
-        <v>-37.745</v>
+        <v>-22.15999999999997</v>
       </c>
       <c r="F65">
-        <v>981.855</v>
+        <v>997.4400000000001</v>
       </c>
       <c r="G65">
         <v>44.5</v>
@@ -6605,28 +6605,28 @@
         <v>154.9666666666667</v>
       </c>
       <c r="M65">
-        <v>74.424609</v>
+        <v>75.60595200000002</v>
       </c>
       <c r="N65">
-        <v>80.54205766666666</v>
+        <v>79.36071466666665</v>
       </c>
       <c r="O65">
-        <v>12.08130865</v>
+        <v>11.9041072</v>
       </c>
       <c r="P65">
-        <v>68.46074901666667</v>
+        <v>67.45660746666665</v>
       </c>
       <c r="Q65">
-        <v>68.66074901666666</v>
+        <v>67.65660746666664</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1032744671459919</v>
+        <v>0.1047731264831934</v>
       </c>
       <c r="T65">
-        <v>1.090269403629917</v>
+        <v>1.118698417467742</v>
       </c>
       <c r="U65">
         <v>0.07580000000000001</v>
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.082196584555341</v>
+        <v>2.049662262921663</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6651,22 +6651,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.07895352553394963</v>
+        <v>0.07910459822388222</v>
       </c>
       <c r="C66">
-        <v>409.2247404246559</v>
+        <v>390.1571899326786</v>
       </c>
       <c r="D66">
-        <v>1362.164740424656</v>
+        <v>1358.682189932679</v>
       </c>
       <c r="E66">
-        <v>-22.15999999999997</v>
+        <v>-6.574999999999932</v>
       </c>
       <c r="F66">
-        <v>997.4400000000001</v>
+        <v>1013.025</v>
       </c>
       <c r="G66">
         <v>44.5</v>
@@ -6687,28 +6687,28 @@
         <v>154.9666666666667</v>
       </c>
       <c r="M66">
-        <v>75.60595200000002</v>
+        <v>76.78729500000001</v>
       </c>
       <c r="N66">
-        <v>79.36071466666665</v>
+        <v>78.17937166666665</v>
       </c>
       <c r="O66">
-        <v>11.9041072</v>
+        <v>11.72690575</v>
       </c>
       <c r="P66">
-        <v>67.45660746666665</v>
+        <v>66.45246591666665</v>
       </c>
       <c r="Q66">
-        <v>67.65660746666664</v>
+        <v>66.65246591666664</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1047731264831934</v>
+        <v>0.1063574234968064</v>
       </c>
       <c r="T66">
-        <v>1.118698417467742</v>
+        <v>1.148751946382015</v>
       </c>
       <c r="U66">
         <v>0.07580000000000001</v>
@@ -6725,7 +6725,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.049662262921663</v>
+        <v>2.018128997338253</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6733,22 +6733,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.07910459822388222</v>
+        <v>0.08722187091381484</v>
       </c>
       <c r="C67">
-        <v>390.1571899326786</v>
+        <v>210.4723840933414</v>
       </c>
       <c r="D67">
-        <v>1358.682189932679</v>
+        <v>1194.582384093341</v>
       </c>
       <c r="E67">
-        <v>-6.574999999999932</v>
+        <v>9.010000000000105</v>
       </c>
       <c r="F67">
-        <v>1013.025</v>
+        <v>1028.61</v>
       </c>
       <c r="G67">
         <v>44.5</v>
@@ -6769,45 +6769,45 @@
         <v>154.9666666666667</v>
       </c>
       <c r="M67">
-        <v>76.78729500000001</v>
+        <v>92.57490000000001</v>
       </c>
       <c r="N67">
-        <v>78.17937166666665</v>
+        <v>62.39176666666665</v>
       </c>
       <c r="O67">
-        <v>11.72690575</v>
+        <v>9.358764999999998</v>
       </c>
       <c r="P67">
-        <v>66.45246591666665</v>
+        <v>53.03300166666666</v>
       </c>
       <c r="Q67">
-        <v>66.65246591666664</v>
+        <v>53.23300166666665</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1063574234968064</v>
+        <v>0.1080349144523966</v>
       </c>
       <c r="T67">
-        <v>1.148751946382015</v>
+        <v>1.180573329938303</v>
       </c>
       <c r="U67">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V67">
         <v>0.15</v>
       </c>
       <c r="W67">
-        <v>0.06443</v>
+        <v>0.0765</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y67">
-        <v>2.018128997338253</v>
+        <v>1.673959860250096</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6815,22 +6815,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.08722187091381484</v>
+        <v>0.08749364360374745</v>
       </c>
       <c r="C68">
-        <v>210.4723840933414</v>
+        <v>190.0762293612922</v>
       </c>
       <c r="D68">
-        <v>1194.582384093341</v>
+        <v>1189.771229361292</v>
       </c>
       <c r="E68">
-        <v>9.010000000000105</v>
+        <v>24.59500000000014</v>
       </c>
       <c r="F68">
-        <v>1028.61</v>
+        <v>1044.195</v>
       </c>
       <c r="G68">
         <v>44.5</v>
@@ -6851,28 +6851,28 @@
         <v>154.9666666666667</v>
       </c>
       <c r="M68">
-        <v>92.57490000000001</v>
+        <v>93.97755000000001</v>
       </c>
       <c r="N68">
-        <v>62.39176666666665</v>
+        <v>60.98911666666666</v>
       </c>
       <c r="O68">
-        <v>9.358764999999998</v>
+        <v>9.148367499999999</v>
       </c>
       <c r="P68">
-        <v>53.03300166666666</v>
+        <v>51.84074916666666</v>
       </c>
       <c r="Q68">
-        <v>53.23300166666665</v>
+        <v>52.04074916666665</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1080349144523966</v>
+        <v>0.1098140715265074</v>
       </c>
       <c r="T68">
-        <v>1.180573329938303</v>
+        <v>1.214323282194973</v>
       </c>
       <c r="U68">
         <v>0.09</v>
@@ -6889,7 +6889,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>1.673959860250096</v>
+        <v>1.648975384723976</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6897,22 +6897,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.08749364360374745</v>
+        <v>0.08776541629368004</v>
       </c>
       <c r="C69">
-        <v>190.0762293612922</v>
+        <v>169.7186728192564</v>
       </c>
       <c r="D69">
-        <v>1189.771229361292</v>
+        <v>1184.998672819256</v>
       </c>
       <c r="E69">
-        <v>24.59500000000014</v>
+        <v>40.17999999999995</v>
       </c>
       <c r="F69">
-        <v>1044.195</v>
+        <v>1059.78</v>
       </c>
       <c r="G69">
         <v>44.5</v>
@@ -6933,28 +6933,28 @@
         <v>154.9666666666667</v>
       </c>
       <c r="M69">
-        <v>93.97755000000001</v>
+        <v>95.38019999999999</v>
       </c>
       <c r="N69">
-        <v>60.98911666666666</v>
+        <v>59.58646666666668</v>
       </c>
       <c r="O69">
-        <v>9.148367499999999</v>
+        <v>8.937970000000002</v>
       </c>
       <c r="P69">
-        <v>51.84074916666666</v>
+        <v>50.64849666666668</v>
       </c>
       <c r="Q69">
-        <v>52.04074916666665</v>
+        <v>50.84849666666667</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1098140715265074</v>
+        <v>0.1117044259177501</v>
       </c>
       <c r="T69">
-        <v>1.214323282194973</v>
+        <v>1.250182606467684</v>
       </c>
       <c r="U69">
         <v>0.09</v>
@@ -6971,7 +6971,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>1.648975384723976</v>
+        <v>1.624725746713329</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6979,22 +6979,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.08776541629368004</v>
+        <v>0.08803718898361265</v>
       </c>
       <c r="C70">
-        <v>169.7186728192564</v>
+        <v>149.3992518335986</v>
       </c>
       <c r="D70">
-        <v>1184.998672819256</v>
+        <v>1180.264251833599</v>
       </c>
       <c r="E70">
-        <v>40.17999999999995</v>
+        <v>55.76499999999999</v>
       </c>
       <c r="F70">
-        <v>1059.78</v>
+        <v>1075.365</v>
       </c>
       <c r="G70">
         <v>44.5</v>
@@ -7015,28 +7015,28 @@
         <v>154.9666666666667</v>
       </c>
       <c r="M70">
-        <v>95.38019999999999</v>
+        <v>96.78285</v>
       </c>
       <c r="N70">
-        <v>59.58646666666668</v>
+        <v>58.18381666666667</v>
       </c>
       <c r="O70">
-        <v>8.937970000000002</v>
+        <v>8.727572500000001</v>
       </c>
       <c r="P70">
-        <v>50.64849666666668</v>
+        <v>49.45624416666667</v>
       </c>
       <c r="Q70">
-        <v>50.84849666666667</v>
+        <v>49.65624416666666</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1117044259177501</v>
+        <v>0.113716738656815</v>
       </c>
       <c r="T70">
-        <v>1.250182606467684</v>
+        <v>1.288355435532184</v>
       </c>
       <c r="U70">
         <v>0.09</v>
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>1.624725746713329</v>
+        <v>1.601178996760962</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7061,22 +7061,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.08803718898361265</v>
+        <v>0.08830896167354527</v>
       </c>
       <c r="C71">
-        <v>149.3992518335986</v>
+        <v>129.1175111346975</v>
       </c>
       <c r="D71">
-        <v>1180.264251833599</v>
+        <v>1175.567511134697</v>
       </c>
       <c r="E71">
-        <v>55.76499999999999</v>
+        <v>71.35000000000002</v>
       </c>
       <c r="F71">
-        <v>1075.365</v>
+        <v>1090.95</v>
       </c>
       <c r="G71">
         <v>44.5</v>
@@ -7097,28 +7097,28 @@
         <v>154.9666666666667</v>
       </c>
       <c r="M71">
-        <v>96.78285</v>
+        <v>98.1855</v>
       </c>
       <c r="N71">
-        <v>58.18381666666667</v>
+        <v>56.78116666666666</v>
       </c>
       <c r="O71">
-        <v>8.727572500000001</v>
+        <v>8.517175</v>
       </c>
       <c r="P71">
-        <v>49.45624416666667</v>
+        <v>48.26399166666666</v>
       </c>
       <c r="Q71">
-        <v>49.65624416666666</v>
+        <v>48.46399166666665</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.113716738656815</v>
+        <v>0.1158632055784842</v>
       </c>
       <c r="T71">
-        <v>1.288355435532184</v>
+        <v>1.32907311986765</v>
       </c>
       <c r="U71">
         <v>0.09</v>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>1.601178996760962</v>
+        <v>1.578305011092948</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7143,22 +7143,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.08830896167354527</v>
+        <v>0.08858073436347785</v>
       </c>
       <c r="C72">
-        <v>129.1175111346975</v>
+        <v>108.8730026710043</v>
       </c>
       <c r="D72">
-        <v>1175.567511134697</v>
+        <v>1170.908002671004</v>
       </c>
       <c r="E72">
-        <v>71.35000000000002</v>
+        <v>86.93500000000006</v>
       </c>
       <c r="F72">
-        <v>1090.95</v>
+        <v>1106.535</v>
       </c>
       <c r="G72">
         <v>44.5</v>
@@ -7179,28 +7179,28 @@
         <v>154.9666666666667</v>
       </c>
       <c r="M72">
-        <v>98.1855</v>
+        <v>99.58815</v>
       </c>
       <c r="N72">
-        <v>56.78116666666666</v>
+        <v>55.37851666666667</v>
       </c>
       <c r="O72">
-        <v>8.517175</v>
+        <v>8.306777500000001</v>
       </c>
       <c r="P72">
-        <v>48.26399166666666</v>
+        <v>47.07173916666667</v>
       </c>
       <c r="Q72">
-        <v>48.46399166666665</v>
+        <v>47.27173916666666</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1158632055784842</v>
+        <v>0.1181577047016478</v>
       </c>
       <c r="T72">
-        <v>1.32907311986765</v>
+        <v>1.372598920364183</v>
       </c>
       <c r="U72">
         <v>0.09</v>
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>1.578305011092948</v>
+        <v>1.556075363049386</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7225,22 +7225,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.08858073436347785</v>
+        <v>0.08885250705341047</v>
       </c>
       <c r="C73">
-        <v>108.8730026710045</v>
+        <v>88.66528546655627</v>
       </c>
       <c r="D73">
-        <v>1170.908002671004</v>
+        <v>1166.285285466556</v>
       </c>
       <c r="E73">
-        <v>86.93499999999983</v>
+        <v>102.5199999999999</v>
       </c>
       <c r="F73">
-        <v>1106.535</v>
+        <v>1122.12</v>
       </c>
       <c r="G73">
         <v>44.5</v>
@@ -7261,28 +7261,28 @@
         <v>154.9666666666667</v>
       </c>
       <c r="M73">
-        <v>99.58814999999998</v>
+        <v>100.9908</v>
       </c>
       <c r="N73">
-        <v>55.37851666666668</v>
+        <v>53.97586666666668</v>
       </c>
       <c r="O73">
-        <v>8.306777500000003</v>
+        <v>8.096380000000002</v>
       </c>
       <c r="P73">
-        <v>47.07173916666668</v>
+        <v>45.87948666666667</v>
       </c>
       <c r="Q73">
-        <v>47.27173916666667</v>
+        <v>46.07948666666666</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1181577047016478</v>
+        <v>0.1206160966193231</v>
       </c>
       <c r="T73">
-        <v>1.372598920364182</v>
+        <v>1.419233706610467</v>
       </c>
       <c r="U73">
         <v>0.09</v>
@@ -7299,7 +7299,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>1.556075363049386</v>
+        <v>1.534463205229255</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7307,22 +7307,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.08885250705341047</v>
+        <v>0.08912427974334307</v>
       </c>
       <c r="C74">
-        <v>88.66528546655627</v>
+        <v>68.49392548185733</v>
       </c>
       <c r="D74">
-        <v>1166.285285466556</v>
+        <v>1161.698925481857</v>
       </c>
       <c r="E74">
-        <v>102.5199999999999</v>
+        <v>118.1049999999999</v>
       </c>
       <c r="F74">
-        <v>1122.12</v>
+        <v>1137.705</v>
       </c>
       <c r="G74">
         <v>44.5</v>
@@ -7343,28 +7343,28 @@
         <v>154.9666666666667</v>
       </c>
       <c r="M74">
-        <v>100.9908</v>
+        <v>102.39345</v>
       </c>
       <c r="N74">
-        <v>53.97586666666668</v>
+        <v>52.57321666666668</v>
       </c>
       <c r="O74">
-        <v>8.096380000000002</v>
+        <v>7.885982500000002</v>
       </c>
       <c r="P74">
-        <v>45.87948666666667</v>
+        <v>44.68723416666668</v>
       </c>
       <c r="Q74">
-        <v>46.07948666666666</v>
+        <v>44.88723416666667</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1206160966193231</v>
+        <v>0.1232565916420114</v>
       </c>
       <c r="T74">
-        <v>1.419233706610467</v>
+        <v>1.469322921467588</v>
       </c>
       <c r="U74">
         <v>0.09</v>
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>1.534463205229255</v>
+        <v>1.513443161322005</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7389,22 +7389,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.08912427974334307</v>
+        <v>0.1267238115136105</v>
       </c>
       <c r="C75">
-        <v>68.49392548185733</v>
+        <v>-356.4193906588162</v>
       </c>
       <c r="D75">
-        <v>1161.698925481857</v>
+        <v>752.3706093411838</v>
       </c>
       <c r="E75">
-        <v>118.1049999999999</v>
+        <v>133.6899999999999</v>
       </c>
       <c r="F75">
-        <v>1137.705</v>
+        <v>1153.29</v>
       </c>
       <c r="G75">
         <v>44.5</v>
@@ -7425,45 +7425,45 @@
         <v>154.9666666666667</v>
       </c>
       <c r="M75">
-        <v>102.39345</v>
+        <v>169.302972</v>
       </c>
       <c r="N75">
-        <v>52.57321666666668</v>
+        <v>-14.33630533333334</v>
       </c>
       <c r="O75">
-        <v>7.885982500000002</v>
+        <v>-2.150445800000001</v>
       </c>
       <c r="P75">
-        <v>44.68723416666668</v>
+        <v>-12.18585953333334</v>
       </c>
       <c r="Q75">
-        <v>44.88723416666667</v>
+        <v>-11.98585953333335</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1232565916420114</v>
+        <v>0.1269492071863031</v>
       </c>
       <c r="T75">
-        <v>1.469322921467588</v>
+        <v>1.539370473836941</v>
       </c>
       <c r="U75">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V75">
-        <v>0.15</v>
+        <v>0.13729823951348</v>
       </c>
       <c r="W75">
-        <v>0.0765</v>
+        <v>0.1266446184394212</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y75">
-        <v>1.513443161322005</v>
+        <v>0.9153215967565334</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7471,22 +7471,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1267238115136105</v>
+        <v>0.1277338115136105</v>
       </c>
       <c r="C76">
-        <v>-356.4193906588162</v>
+        <v>-379.0587524166831</v>
       </c>
       <c r="D76">
-        <v>752.3706093411838</v>
+        <v>745.3162475833169</v>
       </c>
       <c r="E76">
-        <v>133.6899999999999</v>
+        <v>149.275</v>
       </c>
       <c r="F76">
-        <v>1153.29</v>
+        <v>1168.875</v>
       </c>
       <c r="G76">
         <v>44.5</v>
@@ -7507,37 +7507,37 @@
         <v>154.9666666666667</v>
       </c>
       <c r="M76">
-        <v>169.302972</v>
+        <v>171.59085</v>
       </c>
       <c r="N76">
-        <v>-14.33630533333334</v>
+        <v>-16.62418333333335</v>
       </c>
       <c r="O76">
-        <v>-2.150445800000001</v>
+        <v>-2.493627500000002</v>
       </c>
       <c r="P76">
-        <v>-12.18585953333334</v>
+        <v>-14.13055583333335</v>
       </c>
       <c r="Q76">
-        <v>-11.98585953333335</v>
+        <v>-13.93055583333336</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1269492071863031</v>
+        <v>0.1301951754737553</v>
       </c>
       <c r="T76">
-        <v>1.539370473836941</v>
+        <v>1.600945292790419</v>
       </c>
       <c r="U76">
         <v>0.1468</v>
       </c>
       <c r="V76">
-        <v>0.13729823951348</v>
+        <v>0.1354675963199669</v>
       </c>
       <c r="W76">
-        <v>0.1266446184394212</v>
+        <v>0.1269133568602289</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.9153215967565334</v>
+        <v>0.9031173087997796</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7553,22 +7553,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1277338115136105</v>
+        <v>0.1287438115136105</v>
       </c>
       <c r="C77">
-        <v>-379.0587524166831</v>
+        <v>-401.5670570676479</v>
       </c>
       <c r="D77">
-        <v>745.3162475833169</v>
+        <v>738.3929429323522</v>
       </c>
       <c r="E77">
-        <v>149.275</v>
+        <v>164.86</v>
       </c>
       <c r="F77">
-        <v>1168.875</v>
+        <v>1184.46</v>
       </c>
       <c r="G77">
         <v>44.5</v>
@@ -7589,37 +7589,37 @@
         <v>154.9666666666667</v>
       </c>
       <c r="M77">
-        <v>171.59085</v>
+        <v>173.878728</v>
       </c>
       <c r="N77">
-        <v>-16.62418333333335</v>
+        <v>-18.91206133333336</v>
       </c>
       <c r="O77">
-        <v>-2.493627500000002</v>
+        <v>-2.836809200000003</v>
       </c>
       <c r="P77">
-        <v>-14.13055583333335</v>
+        <v>-16.07525213333335</v>
       </c>
       <c r="Q77">
-        <v>-13.93055583333336</v>
+        <v>-15.87525213333336</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1301951754737553</v>
+        <v>0.1337116411184951</v>
       </c>
       <c r="T77">
-        <v>1.600945292790419</v>
+        <v>1.667651346656686</v>
       </c>
       <c r="U77">
         <v>0.1468</v>
       </c>
       <c r="V77">
-        <v>0.1354675963199669</v>
+        <v>0.1336851279473358</v>
       </c>
       <c r="W77">
-        <v>0.1269133568602289</v>
+        <v>0.1271750232173311</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.9031173087997796</v>
+        <v>0.8912341863155719</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7635,22 +7635,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1287438115136105</v>
+        <v>0.1297538115136105</v>
       </c>
       <c r="C78">
-        <v>-401.5670570676479</v>
+        <v>-423.9479231994662</v>
       </c>
       <c r="D78">
-        <v>738.3929429323522</v>
+        <v>731.5970768005338</v>
       </c>
       <c r="E78">
-        <v>164.86</v>
+        <v>180.4450000000001</v>
       </c>
       <c r="F78">
-        <v>1184.46</v>
+        <v>1200.045</v>
       </c>
       <c r="G78">
         <v>44.5</v>
@@ -7671,37 +7671,37 @@
         <v>154.9666666666667</v>
       </c>
       <c r="M78">
-        <v>173.878728</v>
+        <v>176.166606</v>
       </c>
       <c r="N78">
-        <v>-18.91206133333336</v>
+        <v>-21.19993933333336</v>
       </c>
       <c r="O78">
-        <v>-2.836809200000003</v>
+        <v>-3.179990900000004</v>
       </c>
       <c r="P78">
-        <v>-16.07525213333335</v>
+        <v>-18.01994843333336</v>
       </c>
       <c r="Q78">
-        <v>-15.87525213333336</v>
+        <v>-17.81994843333337</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1337116411184951</v>
+        <v>0.1375338863845166</v>
       </c>
       <c r="T78">
-        <v>1.667651346656686</v>
+        <v>1.740157926946107</v>
       </c>
       <c r="U78">
         <v>0.1468</v>
       </c>
       <c r="V78">
-        <v>0.1336851279473358</v>
+        <v>0.1319489574545132</v>
       </c>
       <c r="W78">
-        <v>0.1271750232173311</v>
+        <v>0.1274298930456775</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.8912341863155719</v>
+        <v>0.8796597163634216</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7717,22 +7717,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1297538115136105</v>
+        <v>0.1307638115136105</v>
       </c>
       <c r="C79">
-        <v>-423.9479231994662</v>
+        <v>-446.2048373987811</v>
       </c>
       <c r="D79">
-        <v>731.5970768005338</v>
+        <v>724.925162601219</v>
       </c>
       <c r="E79">
-        <v>180.4450000000001</v>
+        <v>196.0300000000001</v>
       </c>
       <c r="F79">
-        <v>1200.045</v>
+        <v>1215.63</v>
       </c>
       <c r="G79">
         <v>44.5</v>
@@ -7753,37 +7753,37 @@
         <v>154.9666666666667</v>
       </c>
       <c r="M79">
-        <v>176.166606</v>
+        <v>178.454484</v>
       </c>
       <c r="N79">
-        <v>-21.19993933333336</v>
+        <v>-23.48781733333337</v>
       </c>
       <c r="O79">
-        <v>-3.179990900000004</v>
+        <v>-3.523172600000005</v>
       </c>
       <c r="P79">
-        <v>-18.01994843333336</v>
+        <v>-19.96464473333336</v>
       </c>
       <c r="Q79">
-        <v>-17.81994843333337</v>
+        <v>-19.76464473333337</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1375338863845166</v>
+        <v>0.1417036084929037</v>
       </c>
       <c r="T79">
-        <v>1.740157926946107</v>
+        <v>1.819256014534566</v>
       </c>
       <c r="U79">
         <v>0.1468</v>
       </c>
       <c r="V79">
-        <v>0.1319489574545132</v>
+        <v>0.1302573041538143</v>
       </c>
       <c r="W79">
-        <v>0.1274298930456775</v>
+        <v>0.1276782277502201</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.8796597163634216</v>
+        <v>0.8683820276920956</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7799,22 +7799,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1307638115136105</v>
+        <v>0.1317738115136105</v>
       </c>
       <c r="C80">
-        <v>-446.2048373987811</v>
+        <v>-468.3411602157529</v>
       </c>
       <c r="D80">
-        <v>724.925162601219</v>
+        <v>718.3738397842473</v>
       </c>
       <c r="E80">
-        <v>196.0300000000001</v>
+        <v>211.6150000000001</v>
       </c>
       <c r="F80">
-        <v>1215.63</v>
+        <v>1231.215</v>
       </c>
       <c r="G80">
         <v>44.5</v>
@@ -7835,37 +7835,37 @@
         <v>154.9666666666667</v>
       </c>
       <c r="M80">
-        <v>178.454484</v>
+        <v>180.742362</v>
       </c>
       <c r="N80">
-        <v>-23.48781733333337</v>
+        <v>-25.77569533333337</v>
       </c>
       <c r="O80">
-        <v>-3.523172600000005</v>
+        <v>-3.866354300000006</v>
       </c>
       <c r="P80">
-        <v>-19.96464473333336</v>
+        <v>-21.90934103333337</v>
       </c>
       <c r="Q80">
-        <v>-19.76464473333337</v>
+        <v>-21.70934103333338</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1417036084929037</v>
+        <v>0.1462704469925658</v>
       </c>
       <c r="T80">
-        <v>1.819256014534566</v>
+        <v>1.905887253321927</v>
       </c>
       <c r="U80">
         <v>0.1468</v>
       </c>
       <c r="V80">
-        <v>0.1302573041538143</v>
+        <v>0.1286084775189559</v>
       </c>
       <c r="W80">
-        <v>0.1276782277502201</v>
+        <v>0.1279202755002173</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7873,7 +7873,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.8683820276920956</v>
+        <v>0.8573898501263728</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7881,22 +7881,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1317738115136105</v>
+        <v>0.1327838115136105</v>
       </c>
       <c r="C81">
-        <v>-468.3411602157529</v>
+        <v>-490.3601318081593</v>
       </c>
       <c r="D81">
-        <v>718.3738397842473</v>
+        <v>711.9398681918409</v>
       </c>
       <c r="E81">
-        <v>211.6150000000001</v>
+        <v>227.2000000000002</v>
       </c>
       <c r="F81">
-        <v>1231.215</v>
+        <v>1246.8</v>
       </c>
       <c r="G81">
         <v>44.5</v>
@@ -7917,37 +7917,37 @@
         <v>154.9666666666667</v>
       </c>
       <c r="M81">
-        <v>180.742362</v>
+        <v>183.03024</v>
       </c>
       <c r="N81">
-        <v>-25.77569533333337</v>
+        <v>-28.06357333333338</v>
       </c>
       <c r="O81">
-        <v>-3.866354300000006</v>
+        <v>-4.209536000000007</v>
       </c>
       <c r="P81">
-        <v>-21.90934103333337</v>
+        <v>-23.85403733333337</v>
       </c>
       <c r="Q81">
-        <v>-21.70934103333338</v>
+        <v>-23.65403733333338</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1462704469925658</v>
+        <v>0.1512939693421941</v>
       </c>
       <c r="T81">
-        <v>1.905887253321927</v>
+        <v>2.001181615988024</v>
       </c>
       <c r="U81">
         <v>0.1468</v>
       </c>
       <c r="V81">
-        <v>0.1286084775189559</v>
+        <v>0.127000871549969</v>
       </c>
       <c r="W81">
-        <v>0.1279202755002173</v>
+        <v>0.1281562720564646</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.8573898501263728</v>
+        <v>0.8466724769997932</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7963,22 +7963,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1327838115136105</v>
+        <v>0.1337938115136105</v>
       </c>
       <c r="C82">
-        <v>-490.3601318081593</v>
+        <v>-512.2648772848918</v>
       </c>
       <c r="D82">
-        <v>711.9398681918409</v>
+        <v>705.6201227151082</v>
       </c>
       <c r="E82">
-        <v>227.2000000000002</v>
+        <v>242.785</v>
       </c>
       <c r="F82">
-        <v>1246.8</v>
+        <v>1262.385</v>
       </c>
       <c r="G82">
         <v>44.5</v>
@@ -7999,37 +7999,37 @@
         <v>154.9666666666667</v>
       </c>
       <c r="M82">
-        <v>183.03024</v>
+        <v>185.318118</v>
       </c>
       <c r="N82">
-        <v>-28.06357333333338</v>
+        <v>-30.35145133333336</v>
       </c>
       <c r="O82">
-        <v>-4.209536000000007</v>
+        <v>-4.552717700000003</v>
       </c>
       <c r="P82">
-        <v>-23.85403733333337</v>
+        <v>-25.79873363333336</v>
       </c>
       <c r="Q82">
-        <v>-23.65403733333338</v>
+        <v>-25.59873363333337</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1512939693421941</v>
+        <v>0.1568462835180991</v>
       </c>
       <c r="T82">
-        <v>2.001181615988024</v>
+        <v>2.10650696419792</v>
       </c>
       <c r="U82">
         <v>0.1468</v>
       </c>
       <c r="V82">
-        <v>0.127000871549969</v>
+        <v>0.1254329595555249</v>
       </c>
       <c r="W82">
-        <v>0.1281562720564646</v>
+        <v>0.128386441537249</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8037,7 +8037,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.8466724769997932</v>
+        <v>0.8362197303701662</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8045,22 +8045,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1337938115136105</v>
+        <v>0.1348038115136105</v>
       </c>
       <c r="C83">
-        <v>-512.2648772848918</v>
+        <v>-534.0584117673525</v>
       </c>
       <c r="D83">
-        <v>705.6201227151082</v>
+        <v>699.4115882326475</v>
       </c>
       <c r="E83">
-        <v>242.785</v>
+        <v>258.37</v>
       </c>
       <c r="F83">
-        <v>1262.385</v>
+        <v>1277.97</v>
       </c>
       <c r="G83">
         <v>44.5</v>
@@ -8081,37 +8081,37 @@
         <v>154.9666666666667</v>
       </c>
       <c r="M83">
-        <v>185.318118</v>
+        <v>187.605996</v>
       </c>
       <c r="N83">
-        <v>-30.35145133333336</v>
+        <v>-32.63932933333336</v>
       </c>
       <c r="O83">
-        <v>-4.552717700000003</v>
+        <v>-4.895899400000005</v>
       </c>
       <c r="P83">
-        <v>-25.79873363333336</v>
+        <v>-27.74342993333336</v>
       </c>
       <c r="Q83">
-        <v>-25.59873363333337</v>
+        <v>-27.54342993333337</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1568462835180991</v>
+        <v>0.1630155214913268</v>
       </c>
       <c r="T83">
-        <v>2.10650696419792</v>
+        <v>2.223535128875582</v>
       </c>
       <c r="U83">
         <v>0.1468</v>
       </c>
       <c r="V83">
-        <v>0.1254329595555249</v>
+        <v>0.1239032893170429</v>
       </c>
       <c r="W83">
-        <v>0.128386441537249</v>
+        <v>0.1286109971282581</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.8362197303701662</v>
+        <v>0.8260219287802861</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8127,22 +8127,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1348038115136105</v>
+        <v>0.1358138115136105</v>
       </c>
       <c r="C84">
-        <v>-534.0584117673525</v>
+        <v>-555.7436451859822</v>
       </c>
       <c r="D84">
-        <v>699.4115882326475</v>
+        <v>693.3113548140178</v>
       </c>
       <c r="E84">
-        <v>258.37</v>
+        <v>273.955</v>
       </c>
       <c r="F84">
-        <v>1277.97</v>
+        <v>1293.555</v>
       </c>
       <c r="G84">
         <v>44.5</v>
@@ -8163,37 +8163,37 @@
         <v>154.9666666666667</v>
       </c>
       <c r="M84">
-        <v>187.605996</v>
+        <v>189.893874</v>
       </c>
       <c r="N84">
-        <v>-32.63932933333336</v>
+        <v>-34.92720733333337</v>
       </c>
       <c r="O84">
-        <v>-4.895899400000005</v>
+        <v>-5.239081100000005</v>
       </c>
       <c r="P84">
-        <v>-27.74342993333336</v>
+        <v>-29.68812623333336</v>
       </c>
       <c r="Q84">
-        <v>-27.54342993333337</v>
+        <v>-29.48812623333338</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1630155214913268</v>
+        <v>0.1699105521672872</v>
       </c>
       <c r="T84">
-        <v>2.223535128875582</v>
+        <v>2.354331312927087</v>
       </c>
       <c r="U84">
         <v>0.1468</v>
       </c>
       <c r="V84">
-        <v>0.1239032893170429</v>
+        <v>0.1224104786023797</v>
       </c>
       <c r="W84">
-        <v>0.1286109971282581</v>
+        <v>0.1288301417411707</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.8260219287802861</v>
+        <v>0.8160698573491982</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8209,22 +8209,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1358138115136105</v>
+        <v>0.1368238115136105</v>
       </c>
       <c r="C85">
-        <v>-555.7436451859822</v>
+        <v>-577.3233868279478</v>
       </c>
       <c r="D85">
-        <v>693.3113548140178</v>
+        <v>687.3166131720523</v>
       </c>
       <c r="E85">
-        <v>273.955</v>
+        <v>289.5400000000001</v>
       </c>
       <c r="F85">
-        <v>1293.555</v>
+        <v>1309.14</v>
       </c>
       <c r="G85">
         <v>44.5</v>
@@ -8245,37 +8245,37 @@
         <v>154.9666666666667</v>
       </c>
       <c r="M85">
-        <v>189.893874</v>
+        <v>192.181752</v>
       </c>
       <c r="N85">
-        <v>-34.92720733333337</v>
+        <v>-37.21508533333338</v>
       </c>
       <c r="O85">
-        <v>-5.239081100000005</v>
+        <v>-5.582262800000007</v>
       </c>
       <c r="P85">
-        <v>-29.68812623333336</v>
+        <v>-31.63282253333337</v>
       </c>
       <c r="Q85">
-        <v>-29.48812623333338</v>
+        <v>-31.43282253333338</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.1699105521672872</v>
+        <v>0.1776674616777427</v>
       </c>
       <c r="T85">
-        <v>2.354331312927087</v>
+        <v>2.50147701998503</v>
       </c>
       <c r="U85">
         <v>0.1468</v>
       </c>
       <c r="V85">
-        <v>0.1224104786023797</v>
+        <v>0.1209532109999704</v>
       </c>
       <c r="W85">
-        <v>0.1288301417411707</v>
+        <v>0.1290440686252043</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.8160698573491982</v>
+        <v>0.806354739999803</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8291,22 +8291,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1368238115136105</v>
+        <v>0.1843754862821886</v>
       </c>
       <c r="C86">
-        <v>-577.3233868279476</v>
+        <v>-791.7570497802514</v>
       </c>
       <c r="D86">
-        <v>687.3166131720523</v>
+        <v>488.4679502197486</v>
       </c>
       <c r="E86">
-        <v>289.5399999999998</v>
+        <v>305.1249999999999</v>
       </c>
       <c r="F86">
-        <v>1309.14</v>
+        <v>1324.725</v>
       </c>
       <c r="G86">
         <v>44.5</v>
@@ -8327,45 +8327,45 @@
         <v>154.9666666666667</v>
       </c>
       <c r="M86">
-        <v>192.181752</v>
+        <v>266.00478</v>
       </c>
       <c r="N86">
-        <v>-37.21508533333332</v>
+        <v>-111.0381133333333</v>
       </c>
       <c r="O86">
-        <v>-5.582262799999998</v>
+        <v>-16.655717</v>
       </c>
       <c r="P86">
-        <v>-31.63282253333332</v>
+        <v>-94.38239633333332</v>
       </c>
       <c r="Q86">
-        <v>-31.43282253333333</v>
+        <v>-94.18239633333333</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.1776674616777426</v>
+        <v>0.1907364575801133</v>
       </c>
       <c r="T86">
-        <v>2.501477019985029</v>
+        <v>2.749391042960241</v>
       </c>
       <c r="U86">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.1209532109999705</v>
+        <v>0.08738564773159339</v>
       </c>
       <c r="W86">
-        <v>0.1290440686252043</v>
+        <v>0.1832529619354961</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y86">
-        <v>0.8063547399998033</v>
+        <v>0.5825709848772893</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8373,22 +8373,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1843754862821886</v>
+        <v>0.1859254862821886</v>
       </c>
       <c r="C87">
-        <v>-791.7570497802514</v>
+        <v>-811.9054797839922</v>
       </c>
       <c r="D87">
-        <v>488.4679502197486</v>
+        <v>483.9045202160078</v>
       </c>
       <c r="E87">
-        <v>305.1249999999999</v>
+        <v>320.7099999999999</v>
       </c>
       <c r="F87">
-        <v>1324.725</v>
+        <v>1340.31</v>
       </c>
       <c r="G87">
         <v>44.5</v>
@@ -8409,37 +8409,37 @@
         <v>154.9666666666667</v>
       </c>
       <c r="M87">
-        <v>266.00478</v>
+        <v>269.134248</v>
       </c>
       <c r="N87">
-        <v>-111.0381133333333</v>
+        <v>-114.1675813333333</v>
       </c>
       <c r="O87">
-        <v>-16.655717</v>
+        <v>-17.1251372</v>
       </c>
       <c r="P87">
-        <v>-94.38239633333332</v>
+        <v>-97.04244413333335</v>
       </c>
       <c r="Q87">
-        <v>-94.18239633333333</v>
+        <v>-96.84244413333336</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.1907364575801133</v>
+        <v>0.2010890616929785</v>
       </c>
       <c r="T87">
-        <v>2.749391042960241</v>
+        <v>2.945776117457401</v>
       </c>
       <c r="U87">
         <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.08738564773159339</v>
+        <v>0.08636953554866789</v>
       </c>
       <c r="W87">
-        <v>0.1832529619354961</v>
+        <v>0.1834569972618275</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.5825709848772893</v>
+        <v>0.5757969036577859</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8455,22 +8455,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1859254862821886</v>
+        <v>0.1874754862821887</v>
       </c>
       <c r="C88">
-        <v>-811.9054797839922</v>
+        <v>-831.9694328386613</v>
       </c>
       <c r="D88">
-        <v>483.9045202160078</v>
+        <v>479.4255671613387</v>
       </c>
       <c r="E88">
-        <v>320.7099999999999</v>
+        <v>336.295</v>
       </c>
       <c r="F88">
-        <v>1340.31</v>
+        <v>1355.895</v>
       </c>
       <c r="G88">
         <v>44.5</v>
@@ -8491,37 +8491,37 @@
         <v>154.9666666666667</v>
       </c>
       <c r="M88">
-        <v>269.134248</v>
+        <v>272.263716</v>
       </c>
       <c r="N88">
-        <v>-114.1675813333333</v>
+        <v>-117.2970493333333</v>
       </c>
       <c r="O88">
-        <v>-17.1251372</v>
+        <v>-17.5945574</v>
       </c>
       <c r="P88">
-        <v>-97.04244413333335</v>
+        <v>-99.70249193333332</v>
       </c>
       <c r="Q88">
-        <v>-96.84244413333336</v>
+        <v>-99.50249193333333</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2010890616929785</v>
+        <v>0.2130343741309</v>
       </c>
       <c r="T88">
-        <v>2.945776117457401</v>
+        <v>3.17237428033874</v>
       </c>
       <c r="U88">
         <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.08636953554866789</v>
+        <v>0.08537678226649929</v>
       </c>
       <c r="W88">
-        <v>0.1834569972618275</v>
+        <v>0.183656342120887</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.5757969036577859</v>
+        <v>0.5691785484433287</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8537,22 +8537,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1874754862821887</v>
+        <v>0.1890254862821887</v>
       </c>
       <c r="C89">
-        <v>-831.9694328386613</v>
+        <v>-851.9512331524454</v>
       </c>
       <c r="D89">
-        <v>479.4255671613387</v>
+        <v>475.0287668475546</v>
       </c>
       <c r="E89">
-        <v>336.295</v>
+        <v>351.88</v>
       </c>
       <c r="F89">
-        <v>1355.895</v>
+        <v>1371.48</v>
       </c>
       <c r="G89">
         <v>44.5</v>
@@ -8573,37 +8573,37 @@
         <v>154.9666666666667</v>
       </c>
       <c r="M89">
-        <v>272.263716</v>
+        <v>275.393184</v>
       </c>
       <c r="N89">
-        <v>-117.2970493333333</v>
+        <v>-120.4265173333334</v>
       </c>
       <c r="O89">
-        <v>-17.5945574</v>
+        <v>-18.0639776</v>
       </c>
       <c r="P89">
-        <v>-99.70249193333332</v>
+        <v>-102.3625397333333</v>
       </c>
       <c r="Q89">
-        <v>-99.50249193333333</v>
+        <v>-102.1625397333334</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2130343741309</v>
+        <v>0.2269705719751416</v>
       </c>
       <c r="T89">
-        <v>3.17237428033874</v>
+        <v>3.436738803700302</v>
       </c>
       <c r="U89">
         <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.08537678226649929</v>
+        <v>0.08440659155892542</v>
       </c>
       <c r="W89">
-        <v>0.183656342120887</v>
+        <v>0.1838511564149678</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8611,7 +8611,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.5691785484433287</v>
+        <v>0.5627106103928362</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8619,22 +8619,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1890254862821887</v>
+        <v>0.1905754862821886</v>
       </c>
       <c r="C90">
-        <v>-851.9512331524454</v>
+        <v>-871.8531204473252</v>
       </c>
       <c r="D90">
-        <v>475.0287668475546</v>
+        <v>470.7118795526749</v>
       </c>
       <c r="E90">
-        <v>351.88</v>
+        <v>367.465</v>
       </c>
       <c r="F90">
-        <v>1371.48</v>
+        <v>1387.065</v>
       </c>
       <c r="G90">
         <v>44.5</v>
@@ -8655,37 +8655,37 @@
         <v>154.9666666666667</v>
       </c>
       <c r="M90">
-        <v>275.393184</v>
+        <v>278.522652</v>
       </c>
       <c r="N90">
-        <v>-120.4265173333334</v>
+        <v>-123.5559853333333</v>
       </c>
       <c r="O90">
-        <v>-18.0639776</v>
+        <v>-18.5333978</v>
       </c>
       <c r="P90">
-        <v>-102.3625397333333</v>
+        <v>-105.0225875333333</v>
       </c>
       <c r="Q90">
-        <v>-102.1625397333334</v>
+        <v>-104.8225875333333</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2269705719751416</v>
+        <v>0.2434406239728818</v>
       </c>
       <c r="T90">
-        <v>3.436738803700302</v>
+        <v>3.749169604036692</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.08440659155892542</v>
+        <v>0.08345820288972403</v>
       </c>
       <c r="W90">
-        <v>0.1838511564149678</v>
+        <v>0.1840415928597434</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.5627106103928362</v>
+        <v>0.5563880192648269</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8701,22 +8701,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1905754862821886</v>
+        <v>0.1921254862821886</v>
       </c>
       <c r="C91">
-        <v>-871.8531204473252</v>
+        <v>-891.6772537633979</v>
       </c>
       <c r="D91">
-        <v>470.7118795526749</v>
+        <v>466.4727462366023</v>
       </c>
       <c r="E91">
-        <v>367.465</v>
+        <v>383.0500000000001</v>
       </c>
       <c r="F91">
-        <v>1387.065</v>
+        <v>1402.65</v>
       </c>
       <c r="G91">
         <v>44.5</v>
@@ -8737,37 +8737,37 @@
         <v>154.9666666666667</v>
       </c>
       <c r="M91">
-        <v>278.522652</v>
+        <v>281.65212</v>
       </c>
       <c r="N91">
-        <v>-123.5559853333333</v>
+        <v>-126.6854533333334</v>
       </c>
       <c r="O91">
-        <v>-18.5333978</v>
+        <v>-19.002818</v>
       </c>
       <c r="P91">
-        <v>-105.0225875333333</v>
+        <v>-107.6826353333334</v>
       </c>
       <c r="Q91">
-        <v>-104.8225875333333</v>
+        <v>-107.4826353333334</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2434406239728818</v>
+        <v>0.26320468637017</v>
       </c>
       <c r="T91">
-        <v>3.749169604036692</v>
+        <v>4.124086564440363</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.08345820288972403</v>
+        <v>0.08253088952428266</v>
       </c>
       <c r="W91">
-        <v>0.1840415928597434</v>
+        <v>0.184227797383524</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.5563880192648269</v>
+        <v>0.5502059301618842</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8783,22 +8783,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1921254862821886</v>
+        <v>0.1936754862821886</v>
       </c>
       <c r="C92">
-        <v>-891.6772537633979</v>
+        <v>-911.4257150594744</v>
       </c>
       <c r="D92">
-        <v>466.4727462366023</v>
+        <v>462.3092849405257</v>
       </c>
       <c r="E92">
-        <v>383.0500000000001</v>
+        <v>398.6350000000001</v>
       </c>
       <c r="F92">
-        <v>1402.65</v>
+        <v>1418.235</v>
       </c>
       <c r="G92">
         <v>44.5</v>
@@ -8819,37 +8819,37 @@
         <v>154.9666666666667</v>
       </c>
       <c r="M92">
-        <v>281.65212</v>
+        <v>284.7815880000001</v>
       </c>
       <c r="N92">
-        <v>-126.6854533333334</v>
+        <v>-129.8149213333334</v>
       </c>
       <c r="O92">
-        <v>-19.002818</v>
+        <v>-19.47223820000001</v>
       </c>
       <c r="P92">
-        <v>-107.6826353333334</v>
+        <v>-110.3426831333334</v>
       </c>
       <c r="Q92">
-        <v>-107.4826353333334</v>
+        <v>-110.1426831333334</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.26320468637017</v>
+        <v>0.2873607626335222</v>
       </c>
       <c r="T92">
-        <v>4.124086564440363</v>
+        <v>4.582318404933736</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.08253088952428266</v>
+        <v>0.08162395667236745</v>
       </c>
       <c r="W92">
-        <v>0.184227797383524</v>
+        <v>0.1844099095001886</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.5502059301618842</v>
+        <v>0.5441597111491163</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8865,22 +8865,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1936754862821886</v>
+        <v>0.1952254862821887</v>
       </c>
       <c r="C93">
-        <v>-911.4257150594744</v>
+        <v>-931.1005126225596</v>
       </c>
       <c r="D93">
-        <v>462.3092849405257</v>
+        <v>458.2194873774405</v>
       </c>
       <c r="E93">
-        <v>398.6350000000001</v>
+        <v>414.2200000000001</v>
       </c>
       <c r="F93">
-        <v>1418.235</v>
+        <v>1433.82</v>
       </c>
       <c r="G93">
         <v>44.5</v>
@@ -8901,37 +8901,37 @@
         <v>154.9666666666667</v>
       </c>
       <c r="M93">
-        <v>284.7815880000001</v>
+        <v>287.911056</v>
       </c>
       <c r="N93">
-        <v>-129.8149213333334</v>
+        <v>-132.9443893333334</v>
       </c>
       <c r="O93">
-        <v>-19.47223820000001</v>
+        <v>-19.94165840000001</v>
       </c>
       <c r="P93">
-        <v>-110.3426831333334</v>
+        <v>-113.0027309333334</v>
       </c>
       <c r="Q93">
-        <v>-110.1426831333334</v>
+        <v>-112.8027309333334</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.2873607626335222</v>
+        <v>0.3175558579627126</v>
       </c>
       <c r="T93">
-        <v>4.582318404933736</v>
+        <v>5.155108205550455</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.08162395667236745</v>
+        <v>0.08073673975201563</v>
       </c>
       <c r="W93">
-        <v>0.1844099095001886</v>
+        <v>0.1845880626577953</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.5441597111491163</v>
+        <v>0.5382449316801041</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8947,22 +8947,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1952254862821887</v>
+        <v>0.1967754862821886</v>
       </c>
       <c r="C94">
-        <v>-931.1005126225596</v>
+        <v>-950.7035842979467</v>
       </c>
       <c r="D94">
-        <v>458.2194873774405</v>
+        <v>454.2014157020532</v>
       </c>
       <c r="E94">
-        <v>414.2200000000001</v>
+        <v>429.8049999999999</v>
       </c>
       <c r="F94">
-        <v>1433.82</v>
+        <v>1449.405</v>
       </c>
       <c r="G94">
         <v>44.5</v>
@@ -8983,37 +8983,37 @@
         <v>154.9666666666667</v>
       </c>
       <c r="M94">
-        <v>287.911056</v>
+        <v>291.040524</v>
       </c>
       <c r="N94">
-        <v>-132.9443893333334</v>
+        <v>-136.0738573333333</v>
       </c>
       <c r="O94">
-        <v>-19.94165840000001</v>
+        <v>-20.4110786</v>
       </c>
       <c r="P94">
-        <v>-113.0027309333334</v>
+        <v>-115.6627787333333</v>
       </c>
       <c r="Q94">
-        <v>-112.8027309333334</v>
+        <v>-115.4627787333334</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3175558579627126</v>
+        <v>0.3563781233859573</v>
       </c>
       <c r="T94">
-        <v>5.155108205550455</v>
+        <v>5.891552234914807</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.08073673975201563</v>
+        <v>0.07986860276543481</v>
       </c>
       <c r="W94">
-        <v>0.1845880626577953</v>
+        <v>0.1847623845647007</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.5382449316801041</v>
+        <v>0.5324573517695654</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9029,22 +9029,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1967754862821886</v>
+        <v>0.1983254862821886</v>
       </c>
       <c r="C95">
-        <v>-950.7035842979467</v>
+        <v>-970.2368005508467</v>
       </c>
       <c r="D95">
-        <v>454.2014157020532</v>
+        <v>450.2531994491532</v>
       </c>
       <c r="E95">
-        <v>429.8049999999999</v>
+        <v>445.39</v>
       </c>
       <c r="F95">
-        <v>1449.405</v>
+        <v>1464.99</v>
       </c>
       <c r="G95">
         <v>44.5</v>
@@ -9065,37 +9065,37 @@
         <v>154.9666666666667</v>
       </c>
       <c r="M95">
-        <v>291.040524</v>
+        <v>294.169992</v>
       </c>
       <c r="N95">
-        <v>-136.0738573333333</v>
+        <v>-139.2033253333334</v>
       </c>
       <c r="O95">
-        <v>-20.4110786</v>
+        <v>-20.88049880000001</v>
       </c>
       <c r="P95">
-        <v>-115.6627787333333</v>
+        <v>-118.3228265333334</v>
       </c>
       <c r="Q95">
-        <v>-115.4627787333334</v>
+        <v>-118.1228265333334</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.3563781233859573</v>
+        <v>0.4081411439502836</v>
       </c>
       <c r="T95">
-        <v>5.891552234914807</v>
+        <v>6.873477607400609</v>
       </c>
       <c r="U95">
         <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.07986860276543481</v>
+        <v>0.07901893677856849</v>
       </c>
       <c r="W95">
-        <v>0.1847623845647007</v>
+        <v>0.1849329974948634</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.5324573517695654</v>
+        <v>0.5267929118571233</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9111,22 +9111,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1983254862821886</v>
+        <v>0.1998754862821887</v>
       </c>
       <c r="C96">
-        <v>-970.2368005508467</v>
+        <v>-989.7019673697087</v>
       </c>
       <c r="D96">
-        <v>450.2531994491532</v>
+        <v>446.3730326302914</v>
       </c>
       <c r="E96">
-        <v>445.39</v>
+        <v>460.975</v>
       </c>
       <c r="F96">
-        <v>1464.99</v>
+        <v>1480.575</v>
       </c>
       <c r="G96">
         <v>44.5</v>
@@ -9147,37 +9147,37 @@
         <v>154.9666666666667</v>
       </c>
       <c r="M96">
-        <v>294.169992</v>
+        <v>297.29946</v>
       </c>
       <c r="N96">
-        <v>-139.2033253333334</v>
+        <v>-142.3327933333333</v>
       </c>
       <c r="O96">
-        <v>-20.88049880000001</v>
+        <v>-21.349919</v>
       </c>
       <c r="P96">
-        <v>-118.3228265333334</v>
+        <v>-120.9828743333333</v>
       </c>
       <c r="Q96">
-        <v>-118.1228265333334</v>
+        <v>-120.7828743333334</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.4081411439502836</v>
+        <v>0.4806093727403405</v>
       </c>
       <c r="T96">
-        <v>6.873477607400609</v>
+        <v>8.248173128880735</v>
       </c>
       <c r="U96">
         <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.07901893677856849</v>
+        <v>0.07818715849668882</v>
       </c>
       <c r="W96">
-        <v>0.1849329974948634</v>
+        <v>0.1851000185738649</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.5267929118571233</v>
+        <v>0.5212477233112589</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9193,22 +9193,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1998754862821887</v>
+        <v>0.2014254862821886</v>
       </c>
       <c r="C97">
-        <v>-989.7019673697087</v>
+        <v>-1009.100829020704</v>
       </c>
       <c r="D97">
-        <v>446.3730326302914</v>
+        <v>442.5591709792965</v>
       </c>
       <c r="E97">
-        <v>460.975</v>
+        <v>476.5600000000001</v>
       </c>
       <c r="F97">
-        <v>1480.575</v>
+        <v>1496.16</v>
       </c>
       <c r="G97">
         <v>44.5</v>
@@ -9229,37 +9229,37 @@
         <v>154.9666666666667</v>
       </c>
       <c r="M97">
-        <v>297.29946</v>
+        <v>300.428928</v>
       </c>
       <c r="N97">
-        <v>-142.3327933333333</v>
+        <v>-145.4622613333334</v>
       </c>
       <c r="O97">
-        <v>-21.349919</v>
+        <v>-21.81933920000001</v>
       </c>
       <c r="P97">
-        <v>-120.9828743333333</v>
+        <v>-123.6429221333334</v>
       </c>
       <c r="Q97">
-        <v>-120.7828743333334</v>
+        <v>-123.4429221333334</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.4806093727403405</v>
+        <v>0.5893117159254259</v>
       </c>
       <c r="T97">
-        <v>8.248173128880735</v>
+        <v>10.31021641110092</v>
       </c>
       <c r="U97">
         <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.07818715849668882</v>
+        <v>0.07737270892901497</v>
       </c>
       <c r="W97">
-        <v>0.1851000185738649</v>
+        <v>0.1852635600470538</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.5212477233112589</v>
+        <v>0.5158180595267665</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9275,22 +9275,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2014254862821886</v>
+        <v>0.2029754862821886</v>
       </c>
       <c r="C98">
-        <v>-1009.100829020703</v>
+        <v>-1028.435070662197</v>
       </c>
       <c r="D98">
-        <v>442.5591709792967</v>
+        <v>438.8099293378028</v>
       </c>
       <c r="E98">
-        <v>476.5599999999998</v>
+        <v>492.1449999999999</v>
       </c>
       <c r="F98">
-        <v>1496.16</v>
+        <v>1511.745</v>
       </c>
       <c r="G98">
         <v>44.5</v>
@@ -9311,37 +9311,37 @@
         <v>154.9666666666667</v>
       </c>
       <c r="M98">
-        <v>300.428928</v>
+        <v>303.558396</v>
       </c>
       <c r="N98">
-        <v>-145.4622613333333</v>
+        <v>-148.5917293333333</v>
       </c>
       <c r="O98">
-        <v>-21.8193392</v>
+        <v>-22.28875939999999</v>
       </c>
       <c r="P98">
-        <v>-123.6429221333333</v>
+        <v>-126.3029699333333</v>
       </c>
       <c r="Q98">
-        <v>-123.4429221333333</v>
+        <v>-126.1029699333333</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.5893117159254243</v>
+        <v>0.7704822879005658</v>
       </c>
       <c r="T98">
-        <v>10.31021641110089</v>
+        <v>13.7469552148012</v>
       </c>
       <c r="U98">
         <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.07737270892901499</v>
+        <v>0.07657505213593237</v>
       </c>
       <c r="W98">
-        <v>0.1852635600470538</v>
+        <v>0.1854237295311048</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9349,7 +9349,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.5158180595267666</v>
+        <v>0.5105003475728824</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9357,22 +9357,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2029754862821886</v>
+        <v>0.2045254862821887</v>
       </c>
       <c r="C99">
-        <v>-1028.435070662197</v>
+        <v>-1047.706320827443</v>
       </c>
       <c r="D99">
-        <v>438.8099293378028</v>
+        <v>435.1236791725566</v>
       </c>
       <c r="E99">
-        <v>492.1449999999999</v>
+        <v>507.7299999999999</v>
       </c>
       <c r="F99">
-        <v>1511.745</v>
+        <v>1527.33</v>
       </c>
       <c r="G99">
         <v>44.5</v>
@@ -9393,37 +9393,37 @@
         <v>154.9666666666667</v>
       </c>
       <c r="M99">
-        <v>303.558396</v>
+        <v>306.687864</v>
       </c>
       <c r="N99">
-        <v>-148.5917293333333</v>
+        <v>-151.7211973333333</v>
       </c>
       <c r="O99">
-        <v>-22.28875939999999</v>
+        <v>-22.7581796</v>
       </c>
       <c r="P99">
-        <v>-126.3029699333333</v>
+        <v>-128.9630177333333</v>
       </c>
       <c r="Q99">
-        <v>-126.1029699333333</v>
+        <v>-128.7630177333333</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.7704822879005658</v>
+        <v>1.132823431850849</v>
       </c>
       <c r="T99">
-        <v>13.7469552148012</v>
+        <v>20.62043282220179</v>
       </c>
       <c r="U99">
         <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.07657505213593237</v>
+        <v>0.07579367405291264</v>
       </c>
       <c r="W99">
-        <v>0.1854237295311048</v>
+        <v>0.1855806302501752</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.5105003475728824</v>
+        <v>0.505291160352751</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9439,22 +9439,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2045254862821887</v>
+        <v>0.2060754862821886</v>
       </c>
       <c r="C100">
-        <v>-1047.706320827443</v>
+        <v>-1066.916153783185</v>
       </c>
       <c r="D100">
-        <v>435.1236791725566</v>
+        <v>431.4988462168153</v>
       </c>
       <c r="E100">
-        <v>507.7299999999999</v>
+        <v>523.3149999999999</v>
       </c>
       <c r="F100">
-        <v>1527.33</v>
+        <v>1542.915</v>
       </c>
       <c r="G100">
         <v>44.5</v>
@@ -9475,37 +9475,37 @@
         <v>154.9666666666667</v>
       </c>
       <c r="M100">
-        <v>306.687864</v>
+        <v>309.817332</v>
       </c>
       <c r="N100">
-        <v>-151.7211973333333</v>
+        <v>-154.8506653333334</v>
       </c>
       <c r="O100">
-        <v>-22.7581796</v>
+        <v>-23.2275998</v>
       </c>
       <c r="P100">
-        <v>-128.9630177333333</v>
+        <v>-131.6230655333333</v>
       </c>
       <c r="Q100">
-        <v>-128.7630177333333</v>
+        <v>-131.4230655333334</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.132823431850849</v>
+        <v>2.219846863701698</v>
       </c>
       <c r="T100">
-        <v>20.62043282220179</v>
+        <v>41.24086564440358</v>
       </c>
       <c r="U100">
         <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.07579367405291264</v>
+        <v>0.0750280813857115</v>
       </c>
       <c r="W100">
-        <v>0.1855806302501752</v>
+        <v>0.1857343612577491</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9513,91 +9513,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.505291160352751</v>
+        <v>0.5001872092380766</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2060754862821886</v>
-      </c>
-      <c r="C101">
-        <v>-1066.916153783185</v>
-      </c>
-      <c r="D101">
-        <v>431.4988462168153</v>
-      </c>
-      <c r="E101">
-        <v>523.3149999999999</v>
-      </c>
-      <c r="F101">
-        <v>1542.915</v>
-      </c>
-      <c r="G101">
-        <v>44.5</v>
-      </c>
-      <c r="H101">
-        <v>538.9</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>155.1666666666667</v>
-      </c>
-      <c r="K101">
-        <v>0.1999999999999886</v>
-      </c>
-      <c r="L101">
-        <v>154.9666666666667</v>
-      </c>
-      <c r="M101">
-        <v>309.817332</v>
-      </c>
-      <c r="N101">
-        <v>-154.8506653333334</v>
-      </c>
-      <c r="O101">
-        <v>-23.2275998</v>
-      </c>
-      <c r="P101">
-        <v>-131.6230655333333</v>
-      </c>
-      <c r="Q101">
-        <v>-131.4230655333334</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.219846863701698</v>
-      </c>
-      <c r="T101">
-        <v>41.24086564440358</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.0750280813857115</v>
-      </c>
-      <c r="W101">
-        <v>0.1857343612577491</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.5001872092380766</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
